--- a/TDS_simulation_code/ANDES_Dutch_2035_base.xlsx
+++ b/TDS_simulation_code/ANDES_Dutch_2035_base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECE9BAD-63FF-4103-A15F-9650F4500B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A83FA1-8233-46CC-AA4F-BF025EF0B05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -9807,10 +9807,12 @@
         <v>380</v>
       </c>
       <c r="G37" s="34">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H37" s="31">
-        <v>9.8483224013816553E-2</v>
+        <f>TAN(ACOS(0.95))*G37</f>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -9833,10 +9835,12 @@
         <v>380</v>
       </c>
       <c r="G38" s="34">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H38" s="31">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" ref="H38:H46" si="0">TAN(ACOS(0.95))*G38</f>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -9859,10 +9863,12 @@
         <v>380</v>
       </c>
       <c r="G39" s="34">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H39" s="31">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -9885,10 +9891,12 @@
         <v>380</v>
       </c>
       <c r="G40" s="34">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H40" s="31">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -9911,10 +9919,12 @@
         <v>380</v>
       </c>
       <c r="G41" s="34">
-        <v>0.26103399999999999</v>
+        <f>0.261034-0.05+0.18</f>
+        <v>0.39103399999999999</v>
       </c>
       <c r="H41" s="31">
-        <v>8.5797726711259376E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.1285266603845116</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -9937,10 +9947,12 @@
         <v>380</v>
       </c>
       <c r="G42" s="34">
-        <v>0.211034</v>
+        <f>0.211034+0.18</f>
+        <v>0.39103399999999999</v>
       </c>
       <c r="H42" s="31">
-        <v>6.9363521452316224E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.1285266603845116</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -9963,10 +9975,12 @@
         <v>380</v>
       </c>
       <c r="G43" s="31">
-        <v>0.05</v>
+        <f>1.79</f>
+        <v>1.79</v>
       </c>
       <c r="H43" s="31">
-        <v>1.6434205258943162E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.58834454827016514</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -9989,10 +10003,12 @@
         <v>380</v>
       </c>
       <c r="G44" s="34">
-        <v>0.10199</v>
+        <f>0.10199-0.05+0.12</f>
+        <v>0.17198999999999998</v>
       </c>
       <c r="H44" s="31">
-        <v>3.3522491887192259E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.6530379249712673E-2</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -10015,10 +10031,12 @@
         <v>380</v>
       </c>
       <c r="G45" s="31">
-        <v>0.05</v>
+        <f>0.05-0.05+2.05</f>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H45" s="31">
-        <v>1.6434205258943162E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.67380241561666954</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -10041,10 +10059,12 @@
         <v>380</v>
       </c>
       <c r="G46" s="34">
-        <v>0.29962879999999997</v>
+        <f>0.2996288-0.05+0.24</f>
+        <v>0.48962879999999998</v>
       </c>
       <c r="H46" s="31">
-        <v>9.8483224013816553E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.16093320399780056</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -10138,7 +10158,7 @@
         <v>263</v>
       </c>
       <c r="E2">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -10147,19 +10167,18 @@
         <v>38</v>
       </c>
       <c r="I2" s="31">
-        <f>0.1/2</f>
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
         <f>E2/2000</f>
-        <v>0.98599999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-0.98599999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -10187,7 +10206,7 @@
         <v>264</v>
       </c>
       <c r="E3">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="F3">
         <v>380</v>
@@ -10196,26 +10215,25 @@
         <v>39</v>
       </c>
       <c r="I3" s="31">
-        <f t="shared" ref="I3:I7" si="0">0.1/2</f>
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K66" si="1">E3/2000</f>
-        <v>0.98599999999999999</v>
+        <f t="shared" ref="K3:K66" si="0">E3/2000</f>
+        <v>1.17</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L10" si="2">-K3</f>
-        <v>-0.98599999999999999</v>
+        <f t="shared" ref="L3:L10" si="1">-K3</f>
+        <v>-1.17</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M10" si="3">5/2</f>
+        <f t="shared" ref="M3:M10" si="2">5/2</f>
         <v>2.5</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N10" si="4">-M3</f>
+        <f t="shared" ref="N3:N10" si="3">-M3</f>
         <v>-2.5</v>
       </c>
       <c r="O3">
@@ -10236,7 +10254,7 @@
         <v>265</v>
       </c>
       <c r="E4">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="F4">
         <v>380</v>
@@ -10245,26 +10263,25 @@
         <v>41</v>
       </c>
       <c r="I4" s="31">
+        <v>0.24</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+        <v>1.17</v>
+      </c>
+      <c r="L4">
         <f t="shared" si="1"/>
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="L4">
+        <v>-1.17</v>
+      </c>
+      <c r="M4">
         <f t="shared" si="2"/>
-        <v>-0.49299999999999999</v>
-      </c>
-      <c r="M4">
+        <v>2.5</v>
+      </c>
+      <c r="N4">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O4">
@@ -10285,7 +10302,7 @@
         <v>266</v>
       </c>
       <c r="E5">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="F5">
         <v>380</v>
@@ -10294,26 +10311,25 @@
         <v>42</v>
       </c>
       <c r="I5" s="31">
+        <v>0.24</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+        <v>1.17</v>
+      </c>
+      <c r="L5">
         <f t="shared" si="1"/>
-        <v>0.49299999999999999</v>
-      </c>
-      <c r="L5">
+        <v>-1.17</v>
+      </c>
+      <c r="M5">
         <f t="shared" si="2"/>
-        <v>-0.49299999999999999</v>
-      </c>
-      <c r="M5">
+        <v>2.5</v>
+      </c>
+      <c r="N5">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O5">
@@ -10334,7 +10350,7 @@
         <v>267</v>
       </c>
       <c r="E6">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="F6">
         <v>380</v>
@@ -10343,26 +10359,25 @@
         <v>43</v>
       </c>
       <c r="I6" s="31">
+        <v>0.18</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+        <v>0.6</v>
+      </c>
+      <c r="L6">
         <f t="shared" si="1"/>
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="L6">
+        <v>-0.6</v>
+      </c>
+      <c r="M6">
         <f t="shared" si="2"/>
-        <v>-0.56399999999999995</v>
-      </c>
-      <c r="M6">
+        <v>2.5</v>
+      </c>
+      <c r="N6">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O6">
@@ -10383,7 +10398,7 @@
         <v>268</v>
       </c>
       <c r="E7">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="F7">
         <v>380</v>
@@ -10392,26 +10407,25 @@
         <v>44</v>
       </c>
       <c r="I7" s="31">
+        <v>0.18</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.05</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+        <v>0.6</v>
+      </c>
+      <c r="L7">
         <f t="shared" si="1"/>
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="L7">
+        <v>-0.6</v>
+      </c>
+      <c r="M7">
         <f t="shared" si="2"/>
-        <v>-0.56399999999999995</v>
-      </c>
-      <c r="M7">
+        <v>2.5</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O7">
@@ -10432,7 +10446,7 @@
         <v>269</v>
       </c>
       <c r="E8">
-        <v>1000</v>
+        <v>10800</v>
       </c>
       <c r="F8">
         <v>380</v>
@@ -10441,26 +10455,26 @@
         <v>35</v>
       </c>
       <c r="I8" s="34">
-        <f>0.100864/2</f>
-        <v>5.0431999999999998E-2</v>
+        <f>0.100864/2 - 0.05 + 1.79</f>
+        <v>1.790432</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
+        <f t="shared" si="0"/>
+        <v>5.4</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="L8">
+        <v>-5.4</v>
+      </c>
+      <c r="M8">
         <f t="shared" si="2"/>
-        <v>-0.5</v>
-      </c>
-      <c r="M8">
+        <v>2.5</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O8">
@@ -10481,7 +10495,7 @@
         <v>270</v>
       </c>
       <c r="E9">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="F9">
         <v>380</v>
@@ -10490,26 +10504,26 @@
         <v>36</v>
       </c>
       <c r="I9" s="31">
-        <f>0.1/2</f>
-        <v>0.05</v>
+        <f>0.12</f>
+        <v>0.12</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="L9">
+        <v>-0.6</v>
+      </c>
+      <c r="M9">
         <f t="shared" si="2"/>
-        <v>-0.35</v>
-      </c>
-      <c r="M9">
+        <v>2.5</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O9">
@@ -10530,7 +10544,7 @@
         <v>271</v>
       </c>
       <c r="E10" s="10">
-        <v>700</v>
+        <v>11100</v>
       </c>
       <c r="F10" s="10">
         <v>380</v>
@@ -10540,26 +10554,26 @@
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="34">
-        <f>0.49222/2</f>
-        <v>0.24611</v>
+        <f>0.49222/2 - 0.05 + 2.05</f>
+        <v>2.2461099999999998</v>
       </c>
       <c r="J10" s="10">
         <v>0</v>
       </c>
       <c r="K10">
+        <f t="shared" si="0"/>
+        <v>5.55</v>
+      </c>
+      <c r="L10" s="10">
         <f t="shared" si="1"/>
-        <v>0.35</v>
-      </c>
-      <c r="L10" s="10">
+        <v>-5.55</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="2"/>
-        <v>-0.35</v>
-      </c>
-      <c r="M10">
+        <v>2.5</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="3"/>
-        <v>2.5</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O10" s="10">
@@ -10600,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
       <c r="L11">
@@ -10641,25 +10655,25 @@
         <v>28</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I14" si="5">0.6*E12/2000</f>
+        <f t="shared" ref="I12:I14" si="4">0.6*E12/2000</f>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" ref="M12:M75" si="6">0.33*E12/2000</f>
+        <f t="shared" ref="M12:M75" si="5">0.33*E12/2000</f>
         <v>2.0625000000000001E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:N13" si="7">-M12</f>
+        <f t="shared" ref="N12:N13" si="6">-M12</f>
         <v>-2.0625000000000001E-2</v>
       </c>
       <c r="O12">
@@ -10689,25 +10703,25 @@
         <v>29</v>
       </c>
       <c r="I13">
+        <f t="shared" si="4"/>
+        <v>2.1000000000000003E-3</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="0"/>
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <f t="shared" si="5"/>
-        <v>2.1000000000000003E-3</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>3.5000000000000001E-3</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
+        <v>1.155E-3</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="6"/>
-        <v>1.155E-3</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="7"/>
         <v>-1.155E-3</v>
       </c>
       <c r="O13">
@@ -10737,25 +10751,25 @@
         <v>12</v>
       </c>
       <c r="I14">
+        <f t="shared" si="4"/>
+        <v>1.14E-2</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="0"/>
+        <v>1.9E-2</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="5"/>
-        <v>1.14E-2</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
-        <v>1.9E-2</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="6"/>
         <v>6.2700000000000004E-3</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:N77" si="8">-M14</f>
+        <f t="shared" ref="N14:N77" si="7">-M14</f>
         <v>-6.2700000000000004E-3</v>
       </c>
       <c r="O14">
@@ -10792,18 +10806,18 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.24249999999999999</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.0024999999999999E-2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-8.0024999999999999E-2</v>
       </c>
       <c r="O15">
@@ -10840,18 +10854,18 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.4E-2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.92E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.92E-3</v>
       </c>
       <c r="O16" s="5">
@@ -10887,25 +10901,25 @@
         <v>11</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I80" si="9">0.6*E17/2000</f>
+        <f t="shared" ref="I17:I80" si="8">0.6*E17/2000</f>
         <v>0.13650000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.22750000000000001</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.5075000000000003E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.5075000000000003E-2</v>
       </c>
       <c r="O17">
@@ -10935,25 +10949,25 @@
         <v>28</v>
       </c>
       <c r="I18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.25319999999999998</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.42199999999999999</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.13926000000000002</v>
       </c>
       <c r="N18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.13926000000000002</v>
       </c>
       <c r="O18">
@@ -10983,25 +10997,25 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.1599999999999998E-2</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.188E-2</v>
       </c>
       <c r="N19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O19" s="5">
@@ -11037,25 +11051,25 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.1599999999999998E-2</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.5999999999999997E-2</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.188E-2</v>
       </c>
       <c r="N20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O20" s="5">
@@ -11091,25 +11105,25 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.9299999999999995E-2</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.5500000000000003E-2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.1615000000000002E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.1615000000000002E-2</v>
       </c>
       <c r="O21" s="5">
@@ -11145,25 +11159,25 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1077</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9234999999999996E-2</v>
       </c>
       <c r="N22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O22" s="5">
@@ -11199,25 +11213,25 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1077</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9234999999999996E-2</v>
       </c>
       <c r="N23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O23" s="5">
@@ -11253,25 +11267,25 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10829999999999999</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.18049999999999999</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9565000000000007E-2</v>
       </c>
       <c r="N24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9565000000000007E-2</v>
       </c>
       <c r="O24" s="5">
@@ -11307,25 +11321,25 @@
         <v>18</v>
       </c>
       <c r="I25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1077</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17949999999999999</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9234999999999996E-2</v>
       </c>
       <c r="N25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O25">
@@ -11355,25 +11369,25 @@
         <v>18</v>
       </c>
       <c r="I26">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.108</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.9400000000000008E-2</v>
       </c>
       <c r="N26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.9400000000000008E-2</v>
       </c>
       <c r="O26">
@@ -11403,25 +11417,25 @@
         <v>25</v>
       </c>
       <c r="I27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1278</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.0290000000000005E-2</v>
       </c>
       <c r="N27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O27">
@@ -11451,25 +11465,25 @@
         <v>25</v>
       </c>
       <c r="I28">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1245</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.20749999999999999</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.8475000000000008E-2</v>
       </c>
       <c r="N28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O28">
@@ -11499,25 +11513,25 @@
         <v>13</v>
       </c>
       <c r="I29">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.1500000000000002E-2</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.3695000000000001E-2</v>
       </c>
       <c r="N29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.3695000000000001E-2</v>
       </c>
       <c r="O29">
@@ -11547,25 +11561,25 @@
         <v>33</v>
       </c>
       <c r="I30">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.3600000000000005E-2</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.848E-2</v>
       </c>
       <c r="N30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.848E-2</v>
       </c>
       <c r="O30">
@@ -11595,25 +11609,25 @@
         <v>24</v>
       </c>
       <c r="I31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.1999999999999989E-3</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.96E-3</v>
       </c>
       <c r="N31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O31">
@@ -11643,25 +11657,25 @@
         <v>24</v>
       </c>
       <c r="I32">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.1999999999999989E-3</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.96E-3</v>
       </c>
       <c r="N32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O32">
@@ -11691,25 +11705,25 @@
         <v>24</v>
       </c>
       <c r="I33">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.11</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.6300000000000006E-2</v>
       </c>
       <c r="N33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.6300000000000006E-2</v>
       </c>
       <c r="O33">
@@ -11739,25 +11753,25 @@
         <v>28</v>
       </c>
       <c r="I34">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.3699999999999999E-2</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.95E-2</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.3035E-2</v>
       </c>
       <c r="N34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.3035E-2</v>
       </c>
       <c r="O34">
@@ -11787,25 +11801,25 @@
         <v>11</v>
       </c>
       <c r="I35">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1305</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2175</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1775000000000005E-2</v>
       </c>
       <c r="N35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O35">
@@ -11835,25 +11849,25 @@
         <v>11</v>
       </c>
       <c r="I36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1305</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2175</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1775000000000005E-2</v>
       </c>
       <c r="N36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O36">
@@ -11883,25 +11897,25 @@
         <v>22</v>
       </c>
       <c r="I37">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.18</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="N37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O37">
@@ -11931,25 +11945,25 @@
         <v>23</v>
       </c>
       <c r="I38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O38">
@@ -11979,25 +11993,25 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.09</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.9700000000000004E-2</v>
       </c>
       <c r="N39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.9700000000000004E-2</v>
       </c>
       <c r="O39" s="5">
@@ -12033,25 +12047,25 @@
         <v>26</v>
       </c>
       <c r="I40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.192</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.32</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.10560000000000001</v>
       </c>
       <c r="N40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.10560000000000001</v>
       </c>
       <c r="O40">
@@ -12081,25 +12095,25 @@
         <v>26</v>
       </c>
       <c r="I41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.38250000000000001</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.63749999999999996</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.21037500000000001</v>
       </c>
       <c r="N41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-0.21037500000000001</v>
       </c>
       <c r="O41">
@@ -12129,25 +12143,25 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.105</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="L42">
         <v>0</v>
       </c>
       <c r="M42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.7750000000000003E-2</v>
       </c>
       <c r="N42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.7750000000000003E-2</v>
       </c>
       <c r="O42" s="5">
@@ -12183,25 +12197,25 @@
         <v>9</v>
       </c>
       <c r="I43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.89E-2</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.15E-2</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0395000000000001E-2</v>
       </c>
       <c r="N43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O43" s="5">
@@ -12237,25 +12251,25 @@
         <v>9</v>
       </c>
       <c r="I44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.89E-2</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.15E-2</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0395000000000001E-2</v>
       </c>
       <c r="N44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O44" s="5">
@@ -12291,25 +12305,25 @@
         <v>26</v>
       </c>
       <c r="I45">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.9000000000000006E-2</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.115</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7950000000000005E-2</v>
       </c>
       <c r="N45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.7950000000000005E-2</v>
       </c>
       <c r="O45">
@@ -12339,25 +12353,25 @@
         <v>30</v>
       </c>
       <c r="I46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.4450000000000002E-3</v>
       </c>
       <c r="N46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.4450000000000002E-3</v>
       </c>
       <c r="O46">
@@ -12387,25 +12401,25 @@
         <v>16</v>
       </c>
       <c r="I47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.1250000000000002E-3</v>
       </c>
       <c r="N47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-4.1250000000000002E-3</v>
       </c>
       <c r="O47">
@@ -12435,25 +12449,25 @@
         <v>22</v>
       </c>
       <c r="I48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.6E-2</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.28E-3</v>
       </c>
       <c r="N48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O48">
@@ -12483,25 +12497,25 @@
         <v>2</v>
       </c>
       <c r="I49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.8399999999999997E-2</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.112E-2</v>
       </c>
       <c r="N49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.112E-2</v>
       </c>
       <c r="O49" s="5">
@@ -12537,25 +12551,25 @@
         <v>15</v>
       </c>
       <c r="I50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.8599999999999998E-2</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.1E-2</v>
       </c>
       <c r="L50">
         <v>0</v>
       </c>
       <c r="M50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.0230000000000001E-2</v>
       </c>
       <c r="N50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O50">
@@ -12585,25 +12599,25 @@
         <v>15</v>
       </c>
       <c r="I51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.75E-2</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>9.0750000000000015E-3</v>
       </c>
       <c r="N51">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O51">
@@ -12633,25 +12647,25 @@
         <v>15</v>
       </c>
       <c r="I52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.4700000000000003E-2</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.1245</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.1085000000000003E-2</v>
       </c>
       <c r="N52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-4.1085000000000003E-2</v>
       </c>
       <c r="O52">
@@ -12681,25 +12695,25 @@
         <v>12</v>
       </c>
       <c r="I53">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>4.3199999999999995E-2</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.376E-2</v>
       </c>
       <c r="N53">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O53">
@@ -12729,25 +12743,25 @@
         <v>10</v>
       </c>
       <c r="I54">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.4399999999999994E-2</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.124</v>
       </c>
       <c r="L54">
         <v>0</v>
       </c>
       <c r="M54">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>4.0920000000000005E-2</v>
       </c>
       <c r="N54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-4.0920000000000005E-2</v>
       </c>
       <c r="O54">
@@ -12777,25 +12791,25 @@
         <v>10</v>
       </c>
       <c r="I55">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>3.0899999999999997E-2</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5.1499999999999997E-2</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.6995E-2</v>
       </c>
       <c r="N55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.6995E-2</v>
       </c>
       <c r="O55">
@@ -12825,25 +12839,25 @@
         <v>10</v>
       </c>
       <c r="I56">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>6.7500000000000004E-2</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.1125</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7124999999999998E-2</v>
       </c>
       <c r="N56">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.7124999999999998E-2</v>
       </c>
       <c r="O56">
@@ -12873,25 +12887,25 @@
         <v>15</v>
       </c>
       <c r="I57">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>2.0099999999999996E-2</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3500000000000002E-2</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.1054999999999999E-2</v>
       </c>
       <c r="N57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.1054999999999999E-2</v>
       </c>
       <c r="O57">
@@ -12921,25 +12935,25 @@
         <v>12</v>
       </c>
       <c r="I58">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13800000000000001</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.23</v>
       </c>
       <c r="L58">
         <v>0</v>
       </c>
       <c r="M58">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.5900000000000009E-2</v>
       </c>
       <c r="N58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.5900000000000009E-2</v>
       </c>
       <c r="O58">
@@ -12969,25 +12983,25 @@
         <v>12</v>
       </c>
       <c r="I59">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.114</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.19</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.2700000000000006E-2</v>
       </c>
       <c r="N59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-6.2700000000000006E-2</v>
       </c>
       <c r="O59">
@@ -13017,25 +13031,25 @@
         <v>29</v>
       </c>
       <c r="I60">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13200000000000001</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2600000000000012E-2</v>
       </c>
       <c r="N60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2600000000000012E-2</v>
       </c>
       <c r="O60">
@@ -13065,25 +13079,25 @@
         <v>28</v>
       </c>
       <c r="I61">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1278</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.0290000000000005E-2</v>
       </c>
       <c r="N61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O61">
@@ -13113,25 +13127,25 @@
         <v>22</v>
       </c>
       <c r="I62">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.10529999999999999</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.17549999999999999</v>
       </c>
       <c r="L62">
         <v>0</v>
       </c>
       <c r="M62">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.7915000000000008E-2</v>
       </c>
       <c r="N62">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.7915000000000008E-2</v>
       </c>
       <c r="O62">
@@ -13161,25 +13175,25 @@
         <v>22</v>
       </c>
       <c r="I63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1245</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.20749999999999999</v>
       </c>
       <c r="L63">
         <v>0</v>
       </c>
       <c r="M63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>6.8475000000000008E-2</v>
       </c>
       <c r="N63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O63">
@@ -13209,25 +13223,25 @@
         <v>30</v>
       </c>
       <c r="I64">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>7.1999999999999989E-3</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2E-2</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.96E-3</v>
       </c>
       <c r="N64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O64">
@@ -13257,25 +13271,25 @@
         <v>21</v>
       </c>
       <c r="I65">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13109999999999999</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2185</v>
       </c>
       <c r="L65">
         <v>0</v>
       </c>
       <c r="M65">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2105000000000002E-2</v>
       </c>
       <c r="N65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O65">
@@ -13305,25 +13319,25 @@
         <v>21</v>
       </c>
       <c r="I66">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13109999999999999</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0.2185</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2105000000000002E-2</v>
       </c>
       <c r="N66">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O66">
@@ -13353,25 +13367,25 @@
         <v>21</v>
       </c>
       <c r="I67">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.13109999999999999</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67">
-        <f t="shared" ref="K67:K130" si="10">E67/2000</f>
+        <f t="shared" ref="K67:K130" si="9">E67/2000</f>
         <v>0.2185</v>
       </c>
       <c r="L67">
         <v>0</v>
       </c>
       <c r="M67">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.2105000000000002E-2</v>
       </c>
       <c r="N67">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O67">
@@ -13401,25 +13415,25 @@
         <v>15</v>
       </c>
       <c r="I68">
+        <f t="shared" si="8"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
         <f t="shared" si="9"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="10"/>
         <v>0.2175</v>
       </c>
       <c r="L68">
         <v>0</v>
       </c>
       <c r="M68">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>7.1775000000000005E-2</v>
       </c>
       <c r="N68">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O68">
@@ -13449,25 +13463,25 @@
         <v>22</v>
       </c>
       <c r="I69">
+        <f t="shared" si="8"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
         <f t="shared" si="9"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <f t="shared" si="10"/>
         <v>0.06</v>
       </c>
       <c r="L69">
         <v>0</v>
       </c>
       <c r="M69">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="N69">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O69">
@@ -13497,25 +13511,25 @@
         <v>22</v>
       </c>
       <c r="I70">
+        <f t="shared" si="8"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
         <f t="shared" si="9"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <f t="shared" si="10"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.94E-3</v>
       </c>
       <c r="N70">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O70">
@@ -13545,25 +13559,25 @@
         <v>23</v>
       </c>
       <c r="I71">
+        <f t="shared" si="8"/>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
         <f t="shared" si="9"/>
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <f t="shared" si="10"/>
         <v>1.15E-2</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>3.7950000000000002E-3</v>
       </c>
       <c r="N71">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-3.7950000000000002E-3</v>
       </c>
       <c r="O71">
@@ -13593,25 +13607,25 @@
         <v>8</v>
       </c>
       <c r="I72">
+        <f t="shared" si="8"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
         <f t="shared" si="9"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <f t="shared" si="10"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L72">
         <v>0</v>
       </c>
       <c r="M72">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N72">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O72" s="5">
@@ -13647,25 +13661,25 @@
         <v>51</v>
       </c>
       <c r="I73">
+        <f t="shared" si="8"/>
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
         <f t="shared" si="9"/>
-        <v>3.6600000000000001E-2</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <f t="shared" si="10"/>
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>2.0130000000000002E-2</v>
       </c>
       <c r="N73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O73">
@@ -13695,25 +13709,25 @@
         <v>17</v>
       </c>
       <c r="I74">
+        <f t="shared" si="8"/>
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
         <f t="shared" si="9"/>
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <f t="shared" si="10"/>
         <v>1.55E-2</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
       <c r="M74">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>5.1150000000000006E-3</v>
       </c>
       <c r="N74">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.1150000000000006E-3</v>
       </c>
       <c r="O74">
@@ -13743,25 +13757,25 @@
         <v>23</v>
       </c>
       <c r="I75">
+        <f t="shared" si="8"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
         <f t="shared" si="9"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <f t="shared" si="10"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L75">
         <v>0</v>
       </c>
       <c r="M75">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O75">
@@ -13791,25 +13805,25 @@
         <v>8</v>
       </c>
       <c r="I76">
+        <f t="shared" si="8"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
         <f t="shared" si="9"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <f t="shared" si="10"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="L76">
         <v>0</v>
       </c>
       <c r="M76">
-        <f t="shared" ref="M76:M139" si="11">0.33*E76/2000</f>
+        <f t="shared" ref="M76:M139" si="10">0.33*E76/2000</f>
         <v>5.94E-3</v>
       </c>
       <c r="N76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O76" s="5">
@@ -13845,25 +13859,25 @@
         <v>12</v>
       </c>
       <c r="I77">
+        <f t="shared" si="8"/>
+        <v>1.95E-2</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
         <f t="shared" si="9"/>
-        <v>1.95E-2</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
         <f t="shared" si="10"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <f t="shared" si="11"/>
         <v>1.0725E-2</v>
       </c>
       <c r="N77">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O77">
@@ -13893,25 +13907,25 @@
         <v>14</v>
       </c>
       <c r="I78">
+        <f t="shared" si="8"/>
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
         <f t="shared" si="9"/>
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78">
+        <v>1.6E-2</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
         <f t="shared" si="10"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <f t="shared" si="11"/>
         <v>5.28E-3</v>
       </c>
       <c r="N78">
-        <f t="shared" ref="N78:N139" si="12">-M78</f>
+        <f t="shared" ref="N78:N139" si="11">-M78</f>
         <v>-5.28E-3</v>
       </c>
       <c r="O78">
@@ -13941,25 +13955,25 @@
         <v>29</v>
       </c>
       <c r="I79">
+        <f t="shared" si="8"/>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
         <f t="shared" si="9"/>
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
         <f t="shared" si="10"/>
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
+        <v>2.4750000000000001E-2</v>
+      </c>
+      <c r="N79">
         <f t="shared" si="11"/>
-        <v>2.4750000000000001E-2</v>
-      </c>
-      <c r="N79">
-        <f t="shared" si="12"/>
         <v>-2.4750000000000001E-2</v>
       </c>
       <c r="O79">
@@ -13989,25 +14003,25 @@
         <v>51</v>
       </c>
       <c r="I80">
+        <f t="shared" si="8"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
         <f t="shared" si="9"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
-      <c r="K80">
+        <v>0.03</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
         <f t="shared" si="10"/>
-        <v>0.03</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="N80">
         <f t="shared" si="11"/>
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="N80">
-        <f t="shared" si="12"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O80">
@@ -14037,25 +14051,25 @@
         <v>50</v>
       </c>
       <c r="I81">
-        <f t="shared" ref="I81:I82" si="13">0.6*E81/2000</f>
+        <f t="shared" ref="I81:I82" si="12">0.6*E81/2000</f>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
+        <f t="shared" si="9"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
         <f t="shared" si="10"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
+        <v>5.28E-3</v>
+      </c>
+      <c r="N81">
         <f t="shared" si="11"/>
-        <v>5.28E-3</v>
-      </c>
-      <c r="N81">
-        <f t="shared" si="12"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O81">
@@ -14086,25 +14100,25 @@
       </c>
       <c r="H82" s="10"/>
       <c r="I82">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82">
+        <f t="shared" si="9"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L82" s="10">
+        <v>0</v>
+      </c>
+      <c r="M82">
         <f t="shared" si="10"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L82" s="10">
-        <v>0</v>
-      </c>
-      <c r="M82">
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N82">
         <f t="shared" si="11"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N82">
-        <f t="shared" si="12"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O82" s="10">
@@ -14145,18 +14159,18 @@
         <v>0</v>
       </c>
       <c r="K83">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
         <f t="shared" si="10"/>
-        <v>0.3</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="N83">
         <f t="shared" si="11"/>
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="N83">
-        <f t="shared" si="12"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O83">
@@ -14186,25 +14200,25 @@
         <v>13</v>
       </c>
       <c r="I84" s="27">
-        <f t="shared" ref="I84:I109" si="14">0.35*K84</f>
+        <f t="shared" ref="I84:I109" si="13">0.35*K84</f>
         <v>2.2574999999999998E-2</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
+        <f t="shared" si="9"/>
+        <v>6.4500000000000002E-2</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
         <f t="shared" si="10"/>
-        <v>6.4500000000000002E-2</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
+        <v>2.1285000000000002E-2</v>
+      </c>
+      <c r="N84">
         <f t="shared" si="11"/>
-        <v>2.1285000000000002E-2</v>
-      </c>
-      <c r="N84">
-        <f t="shared" si="12"/>
         <v>-2.1285000000000002E-2</v>
       </c>
       <c r="O84">
@@ -14234,25 +14248,25 @@
         <v>12</v>
       </c>
       <c r="I85" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.0999999999999998E-2</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
+        <f t="shared" si="9"/>
+        <v>0.06</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
         <f t="shared" si="10"/>
-        <v>0.06</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="N85">
         <f t="shared" si="11"/>
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="N85">
-        <f t="shared" si="12"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O85">
@@ -14282,25 +14296,25 @@
         <v>12</v>
       </c>
       <c r="I86" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.89E-2</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
+        <f t="shared" si="9"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
         <f t="shared" si="10"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
+        <v>1.7819999999999999E-2</v>
+      </c>
+      <c r="N86">
         <f t="shared" si="11"/>
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="N86">
-        <f t="shared" si="12"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O86">
@@ -14330,25 +14344,25 @@
         <v>15</v>
       </c>
       <c r="I87" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.1349999999999997E-2</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
+        <f t="shared" si="9"/>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
         <f t="shared" si="10"/>
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
+        <v>2.0130000000000002E-2</v>
+      </c>
+      <c r="N87">
         <f t="shared" si="11"/>
-        <v>2.0130000000000002E-2</v>
-      </c>
-      <c r="N87">
-        <f t="shared" si="12"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O87">
@@ -14378,25 +14392,25 @@
         <v>6</v>
       </c>
       <c r="I88" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.9925E-2</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
+        <f t="shared" si="9"/>
+        <v>8.5500000000000007E-2</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
         <f t="shared" si="10"/>
-        <v>8.5500000000000007E-2</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
+        <v>2.8215E-2</v>
+      </c>
+      <c r="N88">
         <f t="shared" si="11"/>
-        <v>2.8215E-2</v>
-      </c>
-      <c r="N88">
-        <f t="shared" si="12"/>
         <v>-2.8215E-2</v>
       </c>
       <c r="O88" s="5">
@@ -14432,25 +14446,25 @@
         <v>5</v>
       </c>
       <c r="I89" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.5199999999999997E-2</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
         <f t="shared" si="10"/>
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
+        <v>2.376E-2</v>
+      </c>
+      <c r="N89">
         <f t="shared" si="11"/>
-        <v>2.376E-2</v>
-      </c>
-      <c r="N89">
-        <f t="shared" si="12"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O89" s="5">
@@ -14486,25 +14500,25 @@
         <v>5</v>
       </c>
       <c r="I90" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4.9874999999999996E-2</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
+        <f t="shared" si="9"/>
+        <v>0.14249999999999999</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
         <f t="shared" si="10"/>
-        <v>0.14249999999999999</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
+        <v>4.7025000000000004E-2</v>
+      </c>
+      <c r="N90">
         <f t="shared" si="11"/>
-        <v>4.7025000000000004E-2</v>
-      </c>
-      <c r="N90">
-        <f t="shared" si="12"/>
         <v>-4.7025000000000004E-2</v>
       </c>
       <c r="O90" s="5">
@@ -14540,25 +14554,25 @@
         <v>28</v>
       </c>
       <c r="I91" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.7849999999999998E-2</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
+        <f t="shared" si="9"/>
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
         <f t="shared" si="10"/>
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
+        <v>1.6830000000000001E-2</v>
+      </c>
+      <c r="N91">
         <f t="shared" si="11"/>
-        <v>1.6830000000000001E-2</v>
-      </c>
-      <c r="N91">
-        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O91">
@@ -14588,25 +14602,25 @@
         <v>30</v>
       </c>
       <c r="I92" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.4437499999999999E-2</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
+        <f t="shared" si="9"/>
+        <v>4.1250000000000002E-2</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
         <f t="shared" si="10"/>
-        <v>4.1250000000000002E-2</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
+        <v>1.3612500000000001E-2</v>
+      </c>
+      <c r="N92">
         <f t="shared" si="11"/>
-        <v>1.3612500000000001E-2</v>
-      </c>
-      <c r="N92">
-        <f t="shared" si="12"/>
         <v>-1.3612500000000001E-2</v>
       </c>
       <c r="O92">
@@ -14636,25 +14650,25 @@
         <v>8</v>
       </c>
       <c r="I93" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.09725E-2</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
+        <f t="shared" si="9"/>
+        <v>3.1350000000000003E-2</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
         <f t="shared" si="10"/>
-        <v>3.1350000000000003E-2</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
+        <v>1.0345500000000001E-2</v>
+      </c>
+      <c r="N93">
         <f t="shared" si="11"/>
-        <v>1.0345500000000001E-2</v>
-      </c>
-      <c r="N93">
-        <f t="shared" si="12"/>
         <v>-1.0345500000000001E-2</v>
       </c>
       <c r="O93" s="5">
@@ -14690,25 +14704,25 @@
         <v>28</v>
       </c>
       <c r="I94" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>8.8199999999999997E-3</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
+        <f t="shared" si="9"/>
+        <v>2.52E-2</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
         <f t="shared" si="10"/>
-        <v>2.52E-2</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
+        <v>8.3160000000000005E-3</v>
+      </c>
+      <c r="N94">
         <f t="shared" si="11"/>
-        <v>8.3160000000000005E-3</v>
-      </c>
-      <c r="N94">
-        <f t="shared" si="12"/>
         <v>-8.3160000000000005E-3</v>
       </c>
       <c r="O94">
@@ -14738,25 +14752,25 @@
         <v>29</v>
       </c>
       <c r="I95" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>5.5299999999999995E-2</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95">
+        <f t="shared" si="9"/>
+        <v>0.158</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
         <f t="shared" si="10"/>
-        <v>0.158</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
+        <v>5.2139999999999999E-2</v>
+      </c>
+      <c r="N95">
         <f t="shared" si="11"/>
-        <v>5.2139999999999999E-2</v>
-      </c>
-      <c r="N95">
-        <f t="shared" si="12"/>
         <v>-5.2139999999999999E-2</v>
       </c>
       <c r="O95">
@@ -14786,25 +14800,25 @@
         <v>4</v>
       </c>
       <c r="I96" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.47E-2</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
+        <f t="shared" si="9"/>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
         <f t="shared" si="10"/>
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
+        <v>1.3860000000000001E-2</v>
+      </c>
+      <c r="N96">
         <f t="shared" si="11"/>
-        <v>1.3860000000000001E-2</v>
-      </c>
-      <c r="N96">
-        <f t="shared" si="12"/>
         <v>-1.3860000000000001E-2</v>
       </c>
       <c r="O96" s="5">
@@ -14840,25 +14854,25 @@
         <v>4</v>
       </c>
       <c r="I97" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.1025E-2</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
+        <f t="shared" si="9"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
         <f t="shared" si="10"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N97">
         <f t="shared" si="11"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N97">
-        <f t="shared" si="12"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O97" s="5">
@@ -14894,25 +14908,25 @@
         <v>29</v>
       </c>
       <c r="I98" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.13685</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98">
+        <f t="shared" si="9"/>
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
         <f t="shared" si="10"/>
-        <v>0.39100000000000001</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
+        <v>0.12903000000000001</v>
+      </c>
+      <c r="N98">
         <f t="shared" si="11"/>
-        <v>0.12903000000000001</v>
-      </c>
-      <c r="N98">
-        <f t="shared" si="12"/>
         <v>-0.12903000000000001</v>
       </c>
       <c r="O98">
@@ -14942,25 +14956,25 @@
         <v>32</v>
       </c>
       <c r="I99" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.14402499999999999</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99">
+        <f t="shared" si="9"/>
+        <v>0.41149999999999998</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
         <f t="shared" si="10"/>
-        <v>0.41149999999999998</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
+        <v>0.13579500000000003</v>
+      </c>
+      <c r="N99">
         <f t="shared" si="11"/>
-        <v>0.13579500000000003</v>
-      </c>
-      <c r="N99">
-        <f t="shared" si="12"/>
         <v>-0.13579500000000003</v>
       </c>
       <c r="O99">
@@ -14990,25 +15004,25 @@
         <v>11</v>
       </c>
       <c r="I100" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.117075</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
+        <f t="shared" si="9"/>
+        <v>0.33450000000000002</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
         <f t="shared" si="10"/>
-        <v>0.33450000000000002</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
+        <v>0.11038500000000001</v>
+      </c>
+      <c r="N100">
         <f t="shared" si="11"/>
-        <v>0.11038500000000001</v>
-      </c>
-      <c r="N100">
-        <f t="shared" si="12"/>
         <v>-0.11038500000000001</v>
       </c>
       <c r="O100">
@@ -15038,25 +15052,25 @@
         <v>25</v>
       </c>
       <c r="I101" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.41475000000000001</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101">
+        <f t="shared" si="9"/>
+        <v>1.1850000000000001</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
         <f t="shared" si="10"/>
-        <v>1.1850000000000001</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
+        <v>0.39105000000000001</v>
+      </c>
+      <c r="N101">
         <f t="shared" si="11"/>
-        <v>0.39105000000000001</v>
-      </c>
-      <c r="N101">
-        <f t="shared" si="12"/>
         <v>-0.39105000000000001</v>
       </c>
       <c r="O101">
@@ -15086,25 +15100,25 @@
         <v>17</v>
       </c>
       <c r="I102" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4.7425000000000002E-2</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
+        <f t="shared" si="9"/>
+        <v>0.13550000000000001</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
         <f t="shared" si="10"/>
-        <v>0.13550000000000001</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
+        <v>4.4715000000000005E-2</v>
+      </c>
+      <c r="N102">
         <f t="shared" si="11"/>
-        <v>4.4715000000000005E-2</v>
-      </c>
-      <c r="N102">
-        <f t="shared" si="12"/>
         <v>-4.4715000000000005E-2</v>
       </c>
       <c r="O102">
@@ -15134,25 +15148,25 @@
         <v>6</v>
       </c>
       <c r="I103" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.17587499999999998</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103">
+        <f t="shared" si="9"/>
+        <v>0.50249999999999995</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
         <f t="shared" si="10"/>
-        <v>0.50249999999999995</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
+        <v>0.16582500000000003</v>
+      </c>
+      <c r="N103">
         <f t="shared" si="11"/>
-        <v>0.16582500000000003</v>
-      </c>
-      <c r="N103">
-        <f t="shared" si="12"/>
         <v>-0.16582500000000003</v>
       </c>
       <c r="O103" s="5">
@@ -15188,25 +15202,25 @@
         <v>3</v>
       </c>
       <c r="I104" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0.118475</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104">
+        <f t="shared" si="9"/>
+        <v>0.33850000000000002</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
         <f t="shared" si="10"/>
-        <v>0.33850000000000002</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
+        <v>0.111705</v>
+      </c>
+      <c r="N104">
         <f t="shared" si="11"/>
-        <v>0.111705</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="12"/>
         <v>-0.111705</v>
       </c>
       <c r="O104" s="5">
@@ -15242,25 +15256,25 @@
         <v>9</v>
       </c>
       <c r="I105" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>5.1974999999999993E-2</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105">
+        <f t="shared" si="9"/>
+        <v>0.14849999999999999</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
         <f t="shared" si="10"/>
-        <v>0.14849999999999999</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
+        <v>4.9005E-2</v>
+      </c>
+      <c r="N105">
         <f t="shared" si="11"/>
-        <v>4.9005E-2</v>
-      </c>
-      <c r="N105">
-        <f t="shared" si="12"/>
         <v>-4.9005E-2</v>
       </c>
       <c r="O105" s="5">
@@ -15296,25 +15310,25 @@
         <v>34</v>
       </c>
       <c r="I106" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.6624999999999997E-2</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
+        <f t="shared" si="9"/>
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
         <f t="shared" si="10"/>
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
+        <v>1.5675000000000001E-2</v>
+      </c>
+      <c r="N106">
         <f t="shared" si="11"/>
-        <v>1.5675000000000001E-2</v>
-      </c>
-      <c r="N106">
-        <f t="shared" si="12"/>
         <v>-1.5675000000000001E-2</v>
       </c>
       <c r="O106">
@@ -15344,25 +15358,25 @@
         <v>26</v>
       </c>
       <c r="I107" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>2.3975E-2</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
+        <f t="shared" si="9"/>
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
         <f t="shared" si="10"/>
-        <v>6.8500000000000005E-2</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
+        <v>2.2605E-2</v>
+      </c>
+      <c r="N107">
         <f t="shared" si="11"/>
-        <v>2.2605E-2</v>
-      </c>
-      <c r="N107">
-        <f t="shared" si="12"/>
         <v>-2.2605E-2</v>
       </c>
       <c r="O107">
@@ -15392,25 +15406,25 @@
         <v>22</v>
       </c>
       <c r="I108" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>8.1375000000000003E-2</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
+        <f t="shared" si="9"/>
+        <v>0.23250000000000001</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
         <f t="shared" si="10"/>
-        <v>0.23250000000000001</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
+        <v>7.6725000000000015E-2</v>
+      </c>
+      <c r="N108">
         <f t="shared" si="11"/>
-        <v>7.6725000000000015E-2</v>
-      </c>
-      <c r="N108">
-        <f t="shared" si="12"/>
         <v>-7.6725000000000015E-2</v>
       </c>
       <c r="O108">
@@ -15440,25 +15454,25 @@
         <v>10</v>
       </c>
       <c r="I109" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>6.474999999999999E-3</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
+        <f t="shared" si="9"/>
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
         <f t="shared" si="10"/>
-        <v>1.8499999999999999E-2</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
+        <v>6.1050000000000002E-3</v>
+      </c>
+      <c r="N109">
         <f t="shared" si="11"/>
-        <v>6.1050000000000002E-3</v>
-      </c>
-      <c r="N109">
-        <f t="shared" si="12"/>
         <v>-6.1050000000000002E-3</v>
       </c>
       <c r="O109">
@@ -15495,18 +15509,18 @@
         <v>0</v>
       </c>
       <c r="K110">
+        <f t="shared" si="9"/>
+        <v>5.5E-2</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
         <f t="shared" si="10"/>
-        <v>5.5E-2</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
+        <v>1.8150000000000003E-2</v>
+      </c>
+      <c r="N110">
         <f t="shared" si="11"/>
-        <v>1.8150000000000003E-2</v>
-      </c>
-      <c r="N110">
-        <f t="shared" si="12"/>
         <v>-1.8150000000000003E-2</v>
       </c>
       <c r="O110" s="5">
@@ -15542,25 +15556,25 @@
         <v>4</v>
       </c>
       <c r="I111" s="28">
-        <f t="shared" ref="I111:I125" si="15">0.1*K111</f>
+        <f t="shared" ref="I111:I125" si="14">0.1*K111</f>
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
+        <f t="shared" si="9"/>
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
         <f t="shared" si="10"/>
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
+        <v>1.6830000000000001E-2</v>
+      </c>
+      <c r="N111">
         <f t="shared" si="11"/>
-        <v>1.6830000000000001E-2</v>
-      </c>
-      <c r="N111">
-        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O111" s="5">
@@ -15596,25 +15610,25 @@
         <v>4</v>
       </c>
       <c r="I112" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112">
+        <f t="shared" si="9"/>
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
         <f t="shared" si="10"/>
-        <v>3.2000000000000001E-2</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
+        <v>1.056E-2</v>
+      </c>
+      <c r="N112">
         <f t="shared" si="11"/>
-        <v>1.056E-2</v>
-      </c>
-      <c r="N112">
-        <f t="shared" si="12"/>
         <v>-1.056E-2</v>
       </c>
       <c r="O112" s="5">
@@ -15650,25 +15664,25 @@
         <v>11</v>
       </c>
       <c r="I113" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>2.725E-3</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113">
+        <f t="shared" si="9"/>
+        <v>2.725E-2</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
         <f t="shared" si="10"/>
-        <v>2.725E-2</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113">
+        <v>8.9925000000000005E-3</v>
+      </c>
+      <c r="N113">
         <f t="shared" si="11"/>
-        <v>8.9925000000000005E-3</v>
-      </c>
-      <c r="N113">
-        <f t="shared" si="12"/>
         <v>-8.9925000000000005E-3</v>
       </c>
       <c r="O113">
@@ -15698,25 +15712,25 @@
         <v>29</v>
       </c>
       <c r="I114" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.36099999999999999</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
+        <f t="shared" si="9"/>
+        <v>3.61</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
         <f t="shared" si="10"/>
-        <v>3.61</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
+        <v>1.1913</v>
+      </c>
+      <c r="N114">
         <f t="shared" si="11"/>
-        <v>1.1913</v>
-      </c>
-      <c r="N114">
-        <f t="shared" si="12"/>
         <v>-1.1913</v>
       </c>
       <c r="O114">
@@ -15746,25 +15760,25 @@
         <v>32</v>
       </c>
       <c r="I115" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.46445000000000003</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
+        <f t="shared" si="9"/>
+        <v>4.6444999999999999</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
         <f t="shared" si="10"/>
-        <v>4.6444999999999999</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
+        <v>1.5326850000000001</v>
+      </c>
+      <c r="N115">
         <f t="shared" si="11"/>
-        <v>1.5326850000000001</v>
-      </c>
-      <c r="N115">
-        <f t="shared" si="12"/>
         <v>-1.5326850000000001</v>
       </c>
       <c r="O115">
@@ -15794,25 +15808,25 @@
         <v>11</v>
       </c>
       <c r="I116" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.15329999999999999</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
+        <f t="shared" si="9"/>
+        <v>1.5329999999999999</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
         <f t="shared" si="10"/>
-        <v>1.5329999999999999</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
+        <v>0.50589000000000006</v>
+      </c>
+      <c r="N116">
         <f t="shared" si="11"/>
-        <v>0.50589000000000006</v>
-      </c>
-      <c r="N116">
-        <f t="shared" si="12"/>
         <v>-0.50589000000000006</v>
       </c>
       <c r="O116">
@@ -15842,25 +15856,25 @@
         <v>25</v>
       </c>
       <c r="I117" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.17660000000000001</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
+        <f t="shared" si="9"/>
+        <v>1.766</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
         <f t="shared" si="10"/>
-        <v>1.766</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
+        <v>0.58277999999999996</v>
+      </c>
+      <c r="N117">
         <f t="shared" si="11"/>
-        <v>0.58277999999999996</v>
-      </c>
-      <c r="N117">
-        <f t="shared" si="12"/>
         <v>-0.58277999999999996</v>
       </c>
       <c r="O117">
@@ -15890,25 +15904,25 @@
         <v>17</v>
       </c>
       <c r="I118" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.52739999999999998</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
+        <f t="shared" si="9"/>
+        <v>5.274</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
         <f t="shared" si="10"/>
-        <v>5.274</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
+        <v>1.7404200000000001</v>
+      </c>
+      <c r="N118">
         <f t="shared" si="11"/>
-        <v>1.7404200000000001</v>
-      </c>
-      <c r="N118">
-        <f t="shared" si="12"/>
         <v>-1.7404200000000001</v>
       </c>
       <c r="O118">
@@ -15938,25 +15952,25 @@
         <v>6</v>
       </c>
       <c r="I119" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.25714999999999999</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119">
+        <f t="shared" si="9"/>
+        <v>2.5714999999999999</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
         <f t="shared" si="10"/>
-        <v>2.5714999999999999</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
+        <v>0.84859499999999999</v>
+      </c>
+      <c r="N119">
         <f t="shared" si="11"/>
-        <v>0.84859499999999999</v>
-      </c>
-      <c r="N119">
-        <f t="shared" si="12"/>
         <v>-0.84859499999999999</v>
       </c>
       <c r="O119" s="5">
@@ -15992,25 +16006,25 @@
         <v>3</v>
       </c>
       <c r="I120" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.19595000000000001</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120">
+        <f t="shared" si="9"/>
+        <v>1.9595</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
         <f t="shared" si="10"/>
-        <v>1.9595</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
+        <v>0.64663499999999996</v>
+      </c>
+      <c r="N120">
         <f t="shared" si="11"/>
-        <v>0.64663499999999996</v>
-      </c>
-      <c r="N120">
-        <f t="shared" si="12"/>
         <v>-0.64663499999999996</v>
       </c>
       <c r="O120" s="5">
@@ -16046,25 +16060,25 @@
         <v>9</v>
       </c>
       <c r="I121" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.25445000000000001</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121">
+        <f t="shared" si="9"/>
+        <v>2.5445000000000002</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
         <f t="shared" si="10"/>
-        <v>2.5445000000000002</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
+        <v>0.83968500000000001</v>
+      </c>
+      <c r="N121">
         <f t="shared" si="11"/>
-        <v>0.83968500000000001</v>
-      </c>
-      <c r="N121">
-        <f t="shared" si="12"/>
         <v>-0.83968500000000001</v>
       </c>
       <c r="O121" s="5">
@@ -16100,25 +16114,25 @@
         <v>34</v>
       </c>
       <c r="I122" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.31505000000000005</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
+        <f t="shared" si="9"/>
+        <v>3.1505000000000001</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
         <f t="shared" si="10"/>
-        <v>3.1505000000000001</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
+        <v>1.0396650000000001</v>
+      </c>
+      <c r="N122">
         <f t="shared" si="11"/>
-        <v>1.0396650000000001</v>
-      </c>
-      <c r="N122">
-        <f t="shared" si="12"/>
         <v>-1.0396650000000001</v>
       </c>
       <c r="O122">
@@ -16148,25 +16162,25 @@
         <v>26</v>
       </c>
       <c r="I123" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.29694999999999999</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123">
+        <f t="shared" si="9"/>
+        <v>2.9695</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
         <f t="shared" si="10"/>
-        <v>2.9695</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
+        <v>0.97993500000000011</v>
+      </c>
+      <c r="N123">
         <f t="shared" si="11"/>
-        <v>0.97993500000000011</v>
-      </c>
-      <c r="N123">
-        <f t="shared" si="12"/>
         <v>-0.97993500000000011</v>
       </c>
       <c r="O123">
@@ -16196,25 +16210,25 @@
         <v>22</v>
       </c>
       <c r="I124" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.65195000000000003</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124">
+        <f t="shared" si="9"/>
+        <v>6.5194999999999999</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
         <f t="shared" si="10"/>
-        <v>6.5194999999999999</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
+        <v>2.1514349999999998</v>
+      </c>
+      <c r="N124">
         <f t="shared" si="11"/>
-        <v>2.1514349999999998</v>
-      </c>
-      <c r="N124">
-        <f t="shared" si="12"/>
         <v>-2.1514349999999998</v>
       </c>
       <c r="O124">
@@ -16244,25 +16258,25 @@
         <v>10</v>
       </c>
       <c r="I125" s="28">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125">
+        <f t="shared" si="9"/>
+        <v>2.13</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
         <f t="shared" si="10"/>
-        <v>2.13</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
+        <v>0.70289999999999997</v>
+      </c>
+      <c r="N125">
         <f t="shared" si="11"/>
-        <v>0.70289999999999997</v>
-      </c>
-      <c r="N125">
-        <f t="shared" si="12"/>
         <v>-0.70289999999999997</v>
       </c>
       <c r="O125">
@@ -16299,18 +16313,18 @@
         <v>0</v>
       </c>
       <c r="K126">
+        <f t="shared" si="9"/>
+        <v>0.38</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
         <f t="shared" si="10"/>
-        <v>0.38</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="N126">
         <f t="shared" si="11"/>
-        <v>0.12540000000000001</v>
-      </c>
-      <c r="N126">
-        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O126">
@@ -16340,25 +16354,25 @@
         <v>28</v>
       </c>
       <c r="I127" s="27">
-        <f t="shared" ref="I127:I143" si="16">0.35*K127</f>
+        <f t="shared" ref="I127:I143" si="15">0.35*K127</f>
         <v>0.13299999999999998</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127">
+        <f t="shared" si="9"/>
+        <v>0.38</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
         <f t="shared" si="10"/>
-        <v>0.38</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
+        <v>0.12540000000000001</v>
+      </c>
+      <c r="N127">
         <f t="shared" si="11"/>
-        <v>0.12540000000000001</v>
-      </c>
-      <c r="N127">
-        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O127">
@@ -16388,25 +16402,25 @@
         <v>12</v>
       </c>
       <c r="I128" s="27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.132825</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
+        <f t="shared" si="9"/>
+        <v>0.3795</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
         <f t="shared" si="10"/>
-        <v>0.3795</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
+        <v>0.12523500000000001</v>
+      </c>
+      <c r="N128">
         <f t="shared" si="11"/>
-        <v>0.12523500000000001</v>
-      </c>
-      <c r="N128">
-        <f t="shared" si="12"/>
         <v>-0.12523500000000001</v>
       </c>
       <c r="O128">
@@ -16436,25 +16450,25 @@
         <v>12</v>
       </c>
       <c r="I129" s="27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.1323</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129">
+        <f t="shared" si="9"/>
+        <v>0.378</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
         <f t="shared" si="10"/>
-        <v>0.378</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
+        <v>0.12474</v>
+      </c>
+      <c r="N129">
         <f t="shared" si="11"/>
-        <v>0.12474</v>
-      </c>
-      <c r="N129">
-        <f t="shared" si="12"/>
         <v>-0.12474</v>
       </c>
       <c r="O129">
@@ -16484,25 +16498,25 @@
         <v>12</v>
       </c>
       <c r="I130" s="27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.12249999999999998</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
+        <f t="shared" si="9"/>
+        <v>0.35</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
         <f t="shared" si="10"/>
-        <v>0.35</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
+        <v>0.11550000000000001</v>
+      </c>
+      <c r="N130">
         <f t="shared" si="11"/>
-        <v>0.11550000000000001</v>
-      </c>
-      <c r="N130">
-        <f t="shared" si="12"/>
         <v>-0.11550000000000001</v>
       </c>
       <c r="O130">
@@ -16532,25 +16546,25 @@
         <v>12</v>
       </c>
       <c r="I131" s="27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0.10149999999999999</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <f t="shared" ref="K131:K171" si="17">E131/2000</f>
+        <f t="shared" ref="K131:K171" si="16">E131/2000</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131">
+        <f t="shared" si="10"/>
+        <v>9.5700000000000007E-2</v>
+      </c>
+      <c r="N131">
         <f t="shared" si="11"/>
-        <v>9.5700000000000007E-2</v>
-      </c>
-      <c r="N131">
-        <f t="shared" si="12"/>
         <v>-9.5700000000000007E-2</v>
       </c>
       <c r="O131">
@@ -16580,25 +16594,25 @@
         <v>11</v>
       </c>
       <c r="I132" s="27">
+        <f t="shared" si="15"/>
+        <v>0.13159999999999999</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
         <f t="shared" si="16"/>
-        <v>0.13159999999999999</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <f t="shared" si="17"/>
         <v>0.376</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132">
+        <f t="shared" si="10"/>
+        <v>0.12408000000000001</v>
+      </c>
+      <c r="N132">
         <f t="shared" si="11"/>
-        <v>0.12408000000000001</v>
-      </c>
-      <c r="N132">
-        <f t="shared" si="12"/>
         <v>-0.12408000000000001</v>
       </c>
       <c r="O132">
@@ -16628,25 +16642,25 @@
         <v>11</v>
       </c>
       <c r="I133" s="27">
+        <f t="shared" si="15"/>
+        <v>0.1280125</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
         <f t="shared" si="16"/>
-        <v>0.1280125</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <f t="shared" si="17"/>
         <v>0.36575000000000002</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133">
+        <f t="shared" si="10"/>
+        <v>0.1206975</v>
+      </c>
+      <c r="N133">
         <f t="shared" si="11"/>
-        <v>0.1206975</v>
-      </c>
-      <c r="N133">
-        <f t="shared" si="12"/>
         <v>-0.1206975</v>
       </c>
       <c r="O133">
@@ -16676,25 +16690,25 @@
         <v>11</v>
       </c>
       <c r="I134" s="27">
+        <f t="shared" si="15"/>
+        <v>3.3249999999999998E-3</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
         <f t="shared" si="16"/>
-        <v>3.3249999999999998E-3</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <f t="shared" si="17"/>
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="M134">
+        <f t="shared" si="10"/>
+        <v>3.1350000000000002E-3</v>
+      </c>
+      <c r="N134">
         <f t="shared" si="11"/>
-        <v>3.1350000000000002E-3</v>
-      </c>
-      <c r="N134">
-        <f t="shared" si="12"/>
         <v>-3.1350000000000002E-3</v>
       </c>
       <c r="O134">
@@ -16724,25 +16738,25 @@
         <v>28</v>
       </c>
       <c r="I135" s="27">
+        <f t="shared" si="15"/>
+        <v>0.35</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
         <f t="shared" si="16"/>
-        <v>0.35</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
+      <c r="N135">
         <f t="shared" si="11"/>
-        <v>0.33</v>
-      </c>
-      <c r="N135">
-        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O135">
@@ -16772,25 +16786,25 @@
         <v>11</v>
       </c>
       <c r="I136" s="27">
+        <f t="shared" si="15"/>
+        <v>0.35</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
         <f t="shared" si="16"/>
-        <v>0.35</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
+      <c r="N136">
         <f t="shared" si="11"/>
-        <v>0.33</v>
-      </c>
-      <c r="N136">
-        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O136">
@@ -16820,25 +16834,25 @@
         <v>28</v>
       </c>
       <c r="I137" s="27">
+        <f t="shared" si="15"/>
+        <v>0.35</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
         <f t="shared" si="16"/>
-        <v>0.35</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137">
+        <f t="shared" si="10"/>
+        <v>0.33</v>
+      </c>
+      <c r="N137">
         <f t="shared" si="11"/>
-        <v>0.33</v>
-      </c>
-      <c r="N137">
-        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O137">
@@ -16868,25 +16882,25 @@
         <v>22</v>
       </c>
       <c r="I138" s="27">
+        <f t="shared" si="15"/>
+        <v>0.52499999999999991</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
         <f t="shared" si="16"/>
-        <v>0.52499999999999991</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138">
+        <f t="shared" si="10"/>
+        <v>0.495</v>
+      </c>
+      <c r="N138">
         <f t="shared" si="11"/>
-        <v>0.495</v>
-      </c>
-      <c r="N138">
-        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O138">
@@ -16916,25 +16930,25 @@
         <v>22</v>
       </c>
       <c r="I139" s="27">
+        <f t="shared" si="15"/>
+        <v>0.52499999999999991</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
         <f t="shared" si="16"/>
-        <v>0.52499999999999991</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139">
+        <f t="shared" si="10"/>
+        <v>0.495</v>
+      </c>
+      <c r="N139">
         <f t="shared" si="11"/>
-        <v>0.495</v>
-      </c>
-      <c r="N139">
-        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O139">
@@ -16964,21 +16978,21 @@
         <v>21</v>
       </c>
       <c r="I140" s="27">
+        <f t="shared" si="15"/>
+        <v>0.7</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
         <f t="shared" si="16"/>
-        <v>0.7</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140">
-        <f t="shared" ref="M140:M171" si="18">0.33*E140/2000</f>
+        <f t="shared" ref="M140:M171" si="17">0.33*E140/2000</f>
         <v>0.66</v>
       </c>
       <c r="N140">
@@ -17012,21 +17026,21 @@
         <v>51</v>
       </c>
       <c r="I141" s="27">
+        <f t="shared" si="15"/>
+        <v>1.3999999999999999E-2</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
         <f t="shared" si="16"/>
-        <v>1.3999999999999999E-2</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
+        <v>0.04</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
         <f t="shared" si="17"/>
-        <v>0.04</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <f t="shared" si="18"/>
         <v>1.3200000000000002E-2</v>
       </c>
       <c r="N141">
@@ -17060,21 +17074,21 @@
         <v>25</v>
       </c>
       <c r="I142" s="27">
+        <f t="shared" si="15"/>
+        <v>1.0499999999999999E-2</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
         <f t="shared" si="16"/>
-        <v>1.0499999999999999E-2</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
+        <v>0.03</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
         <f t="shared" si="17"/>
-        <v>0.03</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <f t="shared" si="18"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N142">
@@ -17108,25 +17122,25 @@
         <v>47</v>
       </c>
       <c r="I143" s="27">
+        <f t="shared" si="15"/>
+        <v>8.7499999999999991E-3</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
         <f t="shared" si="16"/>
-        <v>8.7499999999999991E-3</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
         <f t="shared" si="17"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <f t="shared" si="18"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N143">
-        <f t="shared" ref="N143:N171" si="19">-M143</f>
+        <f t="shared" ref="N143:N171" si="18">-M143</f>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O143">
@@ -17163,18 +17177,18 @@
         <v>0</v>
       </c>
       <c r="K144">
+        <f t="shared" si="16"/>
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
         <f t="shared" si="17"/>
-        <v>4.4499999999999998E-2</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
+        <v>1.4685E-2</v>
+      </c>
+      <c r="N144">
         <f t="shared" si="18"/>
-        <v>1.4685E-2</v>
-      </c>
-      <c r="N144">
-        <f t="shared" si="19"/>
         <v>-1.4685E-2</v>
       </c>
       <c r="O144">
@@ -17204,25 +17218,25 @@
         <v>25</v>
       </c>
       <c r="I145" s="28">
-        <f t="shared" ref="I145:I171" si="20">0.1*K145</f>
+        <f t="shared" ref="I145:I171" si="19">0.1*K145</f>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145">
+        <f t="shared" si="16"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
         <f t="shared" si="17"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N145">
         <f t="shared" si="18"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N145">
-        <f t="shared" si="19"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O145">
@@ -17252,25 +17266,25 @@
         <v>25</v>
       </c>
       <c r="I146" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>7.4000000000000003E-3</v>
       </c>
       <c r="J146">
         <v>0</v>
       </c>
       <c r="K146">
+        <f t="shared" si="16"/>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
         <f t="shared" si="17"/>
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
+        <v>2.4420000000000001E-2</v>
+      </c>
+      <c r="N146">
         <f t="shared" si="18"/>
-        <v>2.4420000000000001E-2</v>
-      </c>
-      <c r="N146">
-        <f t="shared" si="19"/>
         <v>-2.4420000000000001E-2</v>
       </c>
       <c r="O146">
@@ -17300,25 +17314,25 @@
         <v>46</v>
       </c>
       <c r="I147" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.5000000000000005E-3</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147">
+        <f t="shared" si="16"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
         <f t="shared" si="17"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N147">
         <f t="shared" si="18"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N147">
-        <f t="shared" si="19"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O147">
@@ -17348,25 +17362,25 @@
         <v>16</v>
       </c>
       <c r="I148" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148">
+        <f t="shared" si="16"/>
+        <v>0.04</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
         <f t="shared" si="17"/>
-        <v>0.04</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
+        <v>1.3200000000000002E-2</v>
+      </c>
+      <c r="N148">
         <f t="shared" si="18"/>
-        <v>1.3200000000000002E-2</v>
-      </c>
-      <c r="N148">
-        <f t="shared" si="19"/>
         <v>-1.3200000000000002E-2</v>
       </c>
       <c r="O148">
@@ -17396,25 +17410,25 @@
         <v>45</v>
       </c>
       <c r="I149" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.0500000000000002E-3</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149">
+        <f t="shared" si="16"/>
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
         <f t="shared" si="17"/>
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
+        <v>1.0065000000000001E-2</v>
+      </c>
+      <c r="N149">
         <f t="shared" si="18"/>
-        <v>1.0065000000000001E-2</v>
-      </c>
-      <c r="N149">
-        <f t="shared" si="19"/>
         <v>-1.0065000000000001E-2</v>
       </c>
       <c r="O149">
@@ -17451,18 +17465,18 @@
         <v>0</v>
       </c>
       <c r="K150">
+        <f t="shared" si="16"/>
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
         <f t="shared" si="17"/>
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150">
+        <v>1.221E-2</v>
+      </c>
+      <c r="N150">
         <f t="shared" si="18"/>
-        <v>1.221E-2</v>
-      </c>
-      <c r="N150">
-        <f t="shared" si="19"/>
         <v>-1.221E-2</v>
       </c>
       <c r="O150">
@@ -17492,25 +17506,25 @@
         <v>23</v>
       </c>
       <c r="I151" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J151">
         <v>0</v>
       </c>
       <c r="K151">
+        <f t="shared" si="16"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
         <f t="shared" si="17"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151">
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N151">
         <f t="shared" si="18"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N151">
-        <f t="shared" si="19"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O151">
@@ -17540,25 +17554,25 @@
         <v>20</v>
       </c>
       <c r="I152" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152">
+        <f t="shared" si="16"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
         <f t="shared" si="17"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N152">
         <f t="shared" si="18"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N152">
-        <f t="shared" si="19"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O152">
@@ -17588,25 +17602,25 @@
         <v>19</v>
       </c>
       <c r="I153" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.7499999999999999E-3</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153">
+        <f t="shared" si="16"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
         <f t="shared" si="17"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
+        <v>1.2375000000000001E-2</v>
+      </c>
+      <c r="N153">
         <f t="shared" si="18"/>
-        <v>1.2375000000000001E-2</v>
-      </c>
-      <c r="N153">
-        <f t="shared" si="19"/>
         <v>-1.2375000000000001E-2</v>
       </c>
       <c r="O153">
@@ -17636,25 +17650,25 @@
         <v>30</v>
       </c>
       <c r="I154" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="J154">
         <v>0</v>
       </c>
       <c r="K154">
+        <f t="shared" si="16"/>
+        <v>2.7E-2</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
         <f t="shared" si="17"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154">
+        <v>8.9099999999999995E-3</v>
+      </c>
+      <c r="N154">
         <f t="shared" si="18"/>
-        <v>8.9099999999999995E-3</v>
-      </c>
-      <c r="N154">
-        <f t="shared" si="19"/>
         <v>-8.9099999999999995E-3</v>
       </c>
       <c r="O154">
@@ -17684,25 +17698,25 @@
         <v>9</v>
       </c>
       <c r="I155" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.2500000000000003E-3</v>
       </c>
       <c r="J155">
         <v>0</v>
       </c>
       <c r="K155">
+        <f t="shared" si="16"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
         <f t="shared" si="17"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N155">
         <f t="shared" si="18"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N155">
-        <f t="shared" si="19"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O155" s="5">
@@ -17738,25 +17752,25 @@
         <v>50</v>
       </c>
       <c r="I156" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.1000000000000003E-3</v>
       </c>
       <c r="J156">
         <v>0</v>
       </c>
       <c r="K156">
+        <f t="shared" si="16"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
         <f t="shared" si="17"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N156">
         <f t="shared" si="18"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N156">
-        <f t="shared" si="19"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O156">
@@ -17786,25 +17800,25 @@
         <v>27</v>
       </c>
       <c r="I157" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="J157">
         <v>0</v>
       </c>
       <c r="K157">
+        <f t="shared" si="16"/>
+        <v>4.7E-2</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
         <f t="shared" si="17"/>
-        <v>4.7E-2</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157">
+        <v>1.5510000000000001E-2</v>
+      </c>
+      <c r="N157">
         <f t="shared" si="18"/>
-        <v>1.5510000000000001E-2</v>
-      </c>
-      <c r="N157">
-        <f t="shared" si="19"/>
         <v>-1.5510000000000001E-2</v>
       </c>
       <c r="O157">
@@ -17834,25 +17848,25 @@
         <v>20</v>
       </c>
       <c r="I158" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4.8000000000000004E-3</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
       <c r="K158">
+        <f t="shared" si="16"/>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
         <f t="shared" si="17"/>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
+        <v>1.584E-2</v>
+      </c>
+      <c r="N158">
         <f t="shared" si="18"/>
-        <v>1.584E-2</v>
-      </c>
-      <c r="N158">
-        <f t="shared" si="19"/>
         <v>-1.584E-2</v>
       </c>
       <c r="O158">
@@ -17882,25 +17896,25 @@
         <v>27</v>
       </c>
       <c r="I159" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>4.3E-3</v>
       </c>
       <c r="J159">
         <v>0</v>
       </c>
       <c r="K159">
+        <f t="shared" si="16"/>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
         <f t="shared" si="17"/>
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="M159">
+        <v>1.4190000000000001E-2</v>
+      </c>
+      <c r="N159">
         <f t="shared" si="18"/>
-        <v>1.4190000000000001E-2</v>
-      </c>
-      <c r="N159">
-        <f t="shared" si="19"/>
         <v>-1.4190000000000001E-2</v>
       </c>
       <c r="O159">
@@ -17930,25 +17944,25 @@
         <v>47</v>
       </c>
       <c r="I160" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>6.6000000000000008E-3</v>
       </c>
       <c r="J160">
         <v>0</v>
       </c>
       <c r="K160">
+        <f t="shared" si="16"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
         <f t="shared" si="17"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160">
+        <v>2.1780000000000001E-2</v>
+      </c>
+      <c r="N160">
         <f t="shared" si="18"/>
-        <v>2.1780000000000001E-2</v>
-      </c>
-      <c r="N160">
-        <f t="shared" si="19"/>
         <v>-2.1780000000000001E-2</v>
       </c>
       <c r="O160">
@@ -17978,25 +17992,25 @@
         <v>48</v>
       </c>
       <c r="I161" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.2500000000000003E-3</v>
       </c>
       <c r="J161">
         <v>0</v>
       </c>
       <c r="K161">
+        <f t="shared" si="16"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
         <f t="shared" si="17"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161">
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N161">
         <f t="shared" si="18"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N161">
-        <f t="shared" si="19"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O161">
@@ -18026,25 +18040,25 @@
         <v>27</v>
       </c>
       <c r="I162" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>5.8000000000000005E-3</v>
       </c>
       <c r="J162">
         <v>0</v>
       </c>
       <c r="K162">
+        <f t="shared" si="16"/>
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
         <f t="shared" si="17"/>
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162">
+        <v>1.9140000000000001E-2</v>
+      </c>
+      <c r="N162">
         <f t="shared" si="18"/>
-        <v>1.9140000000000001E-2</v>
-      </c>
-      <c r="N162">
-        <f t="shared" si="19"/>
         <v>-1.9140000000000001E-2</v>
       </c>
       <c r="O162">
@@ -18074,25 +18088,25 @@
         <v>9</v>
       </c>
       <c r="I163" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.15E-3</v>
       </c>
       <c r="J163">
         <v>0</v>
       </c>
       <c r="K163">
+        <f t="shared" si="16"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
         <f t="shared" si="17"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="M163">
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N163">
         <f t="shared" si="18"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N163">
-        <f t="shared" si="19"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O163" s="5">
@@ -18128,25 +18142,25 @@
         <v>48</v>
       </c>
       <c r="I164" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.9000000000000002E-3</v>
       </c>
       <c r="J164">
         <v>0</v>
       </c>
       <c r="K164">
+        <f t="shared" si="16"/>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
         <f t="shared" si="17"/>
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164">
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N164">
         <f t="shared" si="18"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N164">
-        <f t="shared" si="19"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O164">
@@ -18176,25 +18190,25 @@
         <v>20</v>
       </c>
       <c r="I165" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>5.7500000000000008E-3</v>
       </c>
       <c r="J165">
         <v>0</v>
       </c>
       <c r="K165">
+        <f t="shared" si="16"/>
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
         <f t="shared" si="17"/>
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="M165">
+        <v>1.8975000000000002E-2</v>
+      </c>
+      <c r="N165">
         <f t="shared" si="18"/>
-        <v>1.8975000000000002E-2</v>
-      </c>
-      <c r="N165">
-        <f t="shared" si="19"/>
         <v>-1.8975000000000002E-2</v>
       </c>
       <c r="O165">
@@ -18224,25 +18238,25 @@
         <v>5</v>
       </c>
       <c r="I166" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>5.4000000000000003E-3</v>
       </c>
       <c r="J166">
         <v>0</v>
       </c>
       <c r="K166">
+        <f t="shared" si="16"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
         <f t="shared" si="17"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166">
+        <v>1.7819999999999999E-2</v>
+      </c>
+      <c r="N166">
         <f t="shared" si="18"/>
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="N166">
-        <f t="shared" si="19"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O166" s="5">
@@ -18278,25 +18292,25 @@
         <v>3</v>
       </c>
       <c r="I167" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.65E-3</v>
       </c>
       <c r="J167">
         <v>0</v>
       </c>
       <c r="K167">
+        <f t="shared" si="16"/>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
         <f t="shared" si="17"/>
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167">
+        <v>8.745000000000001E-3</v>
+      </c>
+      <c r="N167">
         <f t="shared" si="18"/>
-        <v>8.745000000000001E-3</v>
-      </c>
-      <c r="N167">
-        <f t="shared" si="19"/>
         <v>-8.745000000000001E-3</v>
       </c>
       <c r="O167" s="5">
@@ -18332,25 +18346,25 @@
         <v>19</v>
       </c>
       <c r="I168" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.9000000000000002E-3</v>
       </c>
       <c r="J168">
         <v>0</v>
       </c>
       <c r="K168">
+        <f t="shared" si="16"/>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
         <f t="shared" si="17"/>
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="M168">
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N168">
         <f t="shared" si="18"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N168">
-        <f t="shared" si="19"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O168">
@@ -18380,25 +18394,25 @@
         <v>31</v>
       </c>
       <c r="I169" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>3.1000000000000003E-3</v>
       </c>
       <c r="J169">
         <v>0</v>
       </c>
       <c r="K169">
+        <f t="shared" si="16"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
         <f t="shared" si="17"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="M169">
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N169">
         <f t="shared" si="18"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N169">
-        <f t="shared" si="19"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O169">
@@ -18428,25 +18442,25 @@
         <v>31</v>
       </c>
       <c r="I170" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>6.8000000000000005E-3</v>
       </c>
       <c r="J170">
         <v>0</v>
       </c>
       <c r="K170">
+        <f t="shared" si="16"/>
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
         <f t="shared" si="17"/>
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="M170">
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="N170">
         <f t="shared" si="18"/>
-        <v>2.2440000000000002E-2</v>
-      </c>
-      <c r="N170">
-        <f t="shared" si="19"/>
         <v>-2.2440000000000002E-2</v>
       </c>
       <c r="O170">
@@ -18477,25 +18491,25 @@
       </c>
       <c r="H171" s="10"/>
       <c r="I171" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>2.9499999999999999E-3</v>
       </c>
       <c r="J171" s="10">
         <v>0</v>
       </c>
       <c r="K171">
+        <f t="shared" si="16"/>
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="L171" s="10">
+        <v>0</v>
+      </c>
+      <c r="M171">
         <f t="shared" si="17"/>
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="L171" s="10">
-        <v>0</v>
-      </c>
-      <c r="M171">
+        <v>9.7350000000000006E-3</v>
+      </c>
+      <c r="N171">
         <f t="shared" si="18"/>
-        <v>9.7350000000000006E-3</v>
-      </c>
-      <c r="N171">
-        <f t="shared" si="19"/>
         <v>-9.7350000000000006E-3</v>
       </c>
       <c r="O171" s="5">
@@ -18595,7 +18609,7 @@
         <v>272</v>
       </c>
       <c r="E2">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -18604,18 +18618,18 @@
         <v>40</v>
       </c>
       <c r="I2" s="31">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <f>1.972/2</f>
-        <v>0.98599999999999999</v>
+        <f>E2/2000</f>
+        <v>1.17</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-0.98599999999999999</v>
+        <v>-1.17</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -27008,7 +27022,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="J2">
         <v>380</v>
@@ -27052,7 +27066,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1972</v>
+        <v>2340</v>
       </c>
       <c r="J3">
         <v>380</v>
@@ -27096,7 +27110,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="J4">
         <v>380</v>
@@ -27140,7 +27154,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>986</v>
+        <v>2340</v>
       </c>
       <c r="J5">
         <v>380</v>
@@ -27184,7 +27198,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="J6">
         <v>380</v>
@@ -27228,7 +27242,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>1128</v>
+        <v>1200</v>
       </c>
       <c r="J7">
         <v>380</v>
@@ -27272,7 +27286,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>10800</v>
       </c>
       <c r="J8">
         <v>380</v>
@@ -27316,7 +27330,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="J9">
         <v>380</v>
@@ -27362,7 +27376,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10">
-        <v>700</v>
+        <v>11100</v>
       </c>
       <c r="J10" s="10">
         <v>380</v>
@@ -30609,8 +30623,8 @@
       </c>
       <c r="G83" s="23"/>
       <c r="H83" s="23"/>
-      <c r="I83" s="23">
-        <v>1972</v>
+      <c r="I83">
+        <v>2340</v>
       </c>
       <c r="J83" s="23">
         <v>380</v>

--- a/TDS_simulation_code/ANDES_Dutch_2035_base.xlsx
+++ b/TDS_simulation_code/ANDES_Dutch_2035_base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piete\Documents\pieter\school\studie\Master\THESIS\CODE\MPC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0A83FA1-8233-46CC-AA4F-BF025EF0B05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ECE9BAD-63FF-4103-A15F-9650F4500B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="1560" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -9807,12 +9807,10 @@
         <v>380</v>
       </c>
       <c r="G37" s="34">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H37" s="31">
-        <f>TAN(ACOS(0.95))*G37</f>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -9835,12 +9833,10 @@
         <v>380</v>
       </c>
       <c r="G38" s="34">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H38" s="31">
-        <f t="shared" ref="H38:H46" si="0">TAN(ACOS(0.95))*G38</f>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -9863,12 +9859,10 @@
         <v>380</v>
       </c>
       <c r="G39" s="34">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H39" s="31">
-        <f t="shared" si="0"/>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -9891,12 +9885,10 @@
         <v>380</v>
       </c>
       <c r="G40" s="34">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H40" s="31">
-        <f t="shared" si="0"/>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -9919,12 +9911,10 @@
         <v>380</v>
       </c>
       <c r="G41" s="34">
-        <f>0.261034-0.05+0.18</f>
-        <v>0.39103399999999999</v>
+        <v>0.26103399999999999</v>
       </c>
       <c r="H41" s="31">
-        <f t="shared" si="0"/>
-        <v>0.1285266603845116</v>
+        <v>8.5797726711259376E-2</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -9947,12 +9937,10 @@
         <v>380</v>
       </c>
       <c r="G42" s="34">
-        <f>0.211034+0.18</f>
-        <v>0.39103399999999999</v>
+        <v>0.211034</v>
       </c>
       <c r="H42" s="31">
-        <f t="shared" si="0"/>
-        <v>0.1285266603845116</v>
+        <v>6.9363521452316224E-2</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -9975,12 +9963,10 @@
         <v>380</v>
       </c>
       <c r="G43" s="31">
-        <f>1.79</f>
-        <v>1.79</v>
+        <v>0.05</v>
       </c>
       <c r="H43" s="31">
-        <f t="shared" si="0"/>
-        <v>0.58834454827016514</v>
+        <v>1.6434205258943162E-2</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -10003,12 +9989,10 @@
         <v>380</v>
       </c>
       <c r="G44" s="34">
-        <f>0.10199-0.05+0.12</f>
-        <v>0.17198999999999998</v>
+        <v>0.10199</v>
       </c>
       <c r="H44" s="31">
-        <f t="shared" si="0"/>
-        <v>5.6530379249712673E-2</v>
+        <v>3.3522491887192259E-2</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -10031,12 +10015,10 @@
         <v>380</v>
       </c>
       <c r="G45" s="31">
-        <f>0.05-0.05+2.05</f>
-        <v>2.0499999999999998</v>
+        <v>0.05</v>
       </c>
       <c r="H45" s="31">
-        <f t="shared" si="0"/>
-        <v>0.67380241561666954</v>
+        <v>1.6434205258943162E-2</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -10059,12 +10041,10 @@
         <v>380</v>
       </c>
       <c r="G46" s="34">
-        <f>0.2996288-0.05+0.24</f>
-        <v>0.48962879999999998</v>
+        <v>0.29962879999999997</v>
       </c>
       <c r="H46" s="31">
-        <f t="shared" si="0"/>
-        <v>0.16093320399780056</v>
+        <v>9.8483224013816553E-2</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -10158,7 +10138,7 @@
         <v>263</v>
       </c>
       <c r="E2">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -10167,18 +10147,19 @@
         <v>38</v>
       </c>
       <c r="I2" s="31">
-        <v>0.24</v>
+        <f>0.1/2</f>
+        <v>0.05</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
         <f>E2/2000</f>
-        <v>1.17</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-1.17</v>
+        <v>-0.98599999999999999</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -10206,7 +10187,7 @@
         <v>264</v>
       </c>
       <c r="E3">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="F3">
         <v>380</v>
@@ -10215,25 +10196,26 @@
         <v>39</v>
       </c>
       <c r="I3" s="31">
-        <v>0.24</v>
+        <f t="shared" ref="I3:I7" si="0">0.1/2</f>
+        <v>0.05</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K66" si="0">E3/2000</f>
-        <v>1.17</v>
+        <f t="shared" ref="K3:K66" si="1">E3/2000</f>
+        <v>0.98599999999999999</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L10" si="1">-K3</f>
-        <v>-1.17</v>
+        <f t="shared" ref="L3:L10" si="2">-K3</f>
+        <v>-0.98599999999999999</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M10" si="2">5/2</f>
+        <f t="shared" ref="M3:M10" si="3">5/2</f>
         <v>2.5</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N10" si="3">-M3</f>
+        <f t="shared" ref="N3:N10" si="4">-M3</f>
         <v>-2.5</v>
       </c>
       <c r="O3">
@@ -10254,7 +10236,7 @@
         <v>265</v>
       </c>
       <c r="E4">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="F4">
         <v>380</v>
@@ -10263,25 +10245,26 @@
         <v>41</v>
       </c>
       <c r="I4" s="31">
-        <v>0.24</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>1.17</v>
+        <f t="shared" si="1"/>
+        <v>0.49299999999999999</v>
       </c>
       <c r="L4">
-        <f t="shared" si="1"/>
-        <v>-1.17</v>
+        <f t="shared" si="2"/>
+        <v>-0.49299999999999999</v>
       </c>
       <c r="M4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O4">
@@ -10302,7 +10285,7 @@
         <v>266</v>
       </c>
       <c r="E5">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="F5">
         <v>380</v>
@@ -10311,25 +10294,26 @@
         <v>42</v>
       </c>
       <c r="I5" s="31">
-        <v>0.24</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
-        <v>1.17</v>
+        <f t="shared" si="1"/>
+        <v>0.49299999999999999</v>
       </c>
       <c r="L5">
-        <f t="shared" si="1"/>
-        <v>-1.17</v>
+        <f t="shared" si="2"/>
+        <v>-0.49299999999999999</v>
       </c>
       <c r="M5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O5">
@@ -10350,7 +10334,7 @@
         <v>267</v>
       </c>
       <c r="E6">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="F6">
         <v>380</v>
@@ -10359,25 +10343,26 @@
         <v>43</v>
       </c>
       <c r="I6" s="31">
-        <v>0.18</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.56399999999999995</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <f t="shared" si="2"/>
+        <v>-0.56399999999999995</v>
       </c>
       <c r="M6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O6">
@@ -10398,7 +10383,7 @@
         <v>268</v>
       </c>
       <c r="E7">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="F7">
         <v>380</v>
@@ -10407,25 +10392,26 @@
         <v>44</v>
       </c>
       <c r="I7" s="31">
-        <v>0.18</v>
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.56399999999999995</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <f t="shared" si="2"/>
+        <v>-0.56399999999999995</v>
       </c>
       <c r="M7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O7">
@@ -10446,7 +10432,7 @@
         <v>269</v>
       </c>
       <c r="E8">
-        <v>10800</v>
+        <v>1000</v>
       </c>
       <c r="F8">
         <v>380</v>
@@ -10455,26 +10441,26 @@
         <v>35</v>
       </c>
       <c r="I8" s="34">
-        <f>0.100864/2 - 0.05 + 1.79</f>
-        <v>1.790432</v>
+        <f>0.100864/2</f>
+        <v>5.0431999999999998E-2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
-        <v>5.4</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
-        <v>-5.4</v>
+        <f t="shared" si="2"/>
+        <v>-0.5</v>
       </c>
       <c r="M8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O8">
@@ -10495,7 +10481,7 @@
         <v>270</v>
       </c>
       <c r="E9">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="F9">
         <v>380</v>
@@ -10504,26 +10490,26 @@
         <v>36</v>
       </c>
       <c r="I9" s="31">
-        <f>0.12</f>
-        <v>0.12</v>
+        <f>0.1/2</f>
+        <v>0.05</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <f t="shared" si="1"/>
+        <v>0.35</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
-        <v>-0.6</v>
+        <f t="shared" si="2"/>
+        <v>-0.35</v>
       </c>
       <c r="M9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O9">
@@ -10544,7 +10530,7 @@
         <v>271</v>
       </c>
       <c r="E10" s="10">
-        <v>11100</v>
+        <v>700</v>
       </c>
       <c r="F10" s="10">
         <v>380</v>
@@ -10554,26 +10540,26 @@
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="34">
-        <f>0.49222/2 - 0.05 + 2.05</f>
-        <v>2.2461099999999998</v>
+        <f>0.49222/2</f>
+        <v>0.24611</v>
       </c>
       <c r="J10" s="10">
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="0"/>
-        <v>5.55</v>
+        <f t="shared" si="1"/>
+        <v>0.35</v>
       </c>
       <c r="L10" s="10">
-        <f t="shared" si="1"/>
-        <v>-5.55</v>
+        <f t="shared" si="2"/>
+        <v>-0.35</v>
       </c>
       <c r="M10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.5</v>
       </c>
       <c r="N10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.5</v>
       </c>
       <c r="O10" s="10">
@@ -10614,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="L11">
@@ -10655,25 +10641,25 @@
         <v>28</v>
       </c>
       <c r="I12">
-        <f t="shared" ref="I12:I14" si="4">0.6*E12/2000</f>
+        <f t="shared" ref="I12:I14" si="5">0.6*E12/2000</f>
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.25E-2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <f t="shared" ref="M12:M75" si="5">0.33*E12/2000</f>
+        <f t="shared" ref="M12:M75" si="6">0.33*E12/2000</f>
         <v>2.0625000000000001E-2</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:N13" si="6">-M12</f>
+        <f t="shared" ref="N12:N13" si="7">-M12</f>
         <v>-2.0625000000000001E-2</v>
       </c>
       <c r="O12">
@@ -10703,25 +10689,25 @@
         <v>29</v>
       </c>
       <c r="I13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.1000000000000003E-3</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.155E-3</v>
       </c>
       <c r="N13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-1.155E-3</v>
       </c>
       <c r="O13">
@@ -10751,25 +10737,25 @@
         <v>12</v>
       </c>
       <c r="I14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.14E-2</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.9E-2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.2700000000000004E-3</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:N77" si="7">-M14</f>
+        <f t="shared" ref="N14:N77" si="8">-M14</f>
         <v>-6.2700000000000004E-3</v>
       </c>
       <c r="O14">
@@ -10806,18 +10792,18 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.24249999999999999</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.0024999999999999E-2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-8.0024999999999999E-2</v>
       </c>
       <c r="O15">
@@ -10854,18 +10840,18 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4E-2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.92E-3</v>
       </c>
       <c r="N16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-7.92E-3</v>
       </c>
       <c r="O16" s="5">
@@ -10901,25 +10887,25 @@
         <v>11</v>
       </c>
       <c r="I17">
-        <f t="shared" ref="I17:I80" si="8">0.6*E17/2000</f>
+        <f t="shared" ref="I17:I80" si="9">0.6*E17/2000</f>
         <v>0.13650000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.22750000000000001</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.5075000000000003E-2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>-7.5075000000000003E-2</v>
       </c>
       <c r="O17">
@@ -10949,25 +10935,25 @@
         <v>28</v>
       </c>
       <c r="I18">
+        <f t="shared" si="9"/>
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>0.42199999999999999</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="6"/>
+        <v>0.13926000000000002</v>
+      </c>
+      <c r="N18">
         <f t="shared" si="8"/>
-        <v>0.25319999999999998</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>0.42199999999999999</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="5"/>
-        <v>0.13926000000000002</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="7"/>
         <v>-0.13926000000000002</v>
       </c>
       <c r="O18">
@@ -10997,25 +10983,25 @@
         <v>3</v>
       </c>
       <c r="I19">
+        <f t="shared" si="9"/>
+        <v>2.1599999999999998E-2</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="6"/>
+        <v>1.188E-2</v>
+      </c>
+      <c r="N19">
         <f t="shared" si="8"/>
-        <v>2.1599999999999998E-2</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="5"/>
-        <v>1.188E-2</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O19" s="5">
@@ -11051,25 +11037,25 @@
         <v>3</v>
       </c>
       <c r="I20">
+        <f t="shared" si="9"/>
+        <v>2.1599999999999998E-2</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="6"/>
+        <v>1.188E-2</v>
+      </c>
+      <c r="N20">
         <f t="shared" si="8"/>
-        <v>2.1599999999999998E-2</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="5"/>
-        <v>1.188E-2</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="7"/>
         <v>-1.188E-2</v>
       </c>
       <c r="O20" s="5">
@@ -11105,25 +11091,25 @@
         <v>6</v>
       </c>
       <c r="I21">
+        <f t="shared" si="9"/>
+        <v>3.9299999999999995E-2</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>6.5500000000000003E-2</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="6"/>
+        <v>2.1615000000000002E-2</v>
+      </c>
+      <c r="N21">
         <f t="shared" si="8"/>
-        <v>3.9299999999999995E-2</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="0"/>
-        <v>6.5500000000000003E-2</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="5"/>
-        <v>2.1615000000000002E-2</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="7"/>
         <v>-2.1615000000000002E-2</v>
       </c>
       <c r="O21" s="5">
@@ -11159,25 +11145,25 @@
         <v>6</v>
       </c>
       <c r="I22">
+        <f t="shared" si="9"/>
+        <v>0.1077</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="6"/>
+        <v>5.9234999999999996E-2</v>
+      </c>
+      <c r="N22">
         <f t="shared" si="8"/>
-        <v>0.1077</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>0.17949999999999999</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="5"/>
-        <v>5.9234999999999996E-2</v>
-      </c>
-      <c r="N22">
-        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O22" s="5">
@@ -11213,25 +11199,25 @@
         <v>6</v>
       </c>
       <c r="I23">
+        <f t="shared" si="9"/>
+        <v>0.1077</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="6"/>
+        <v>5.9234999999999996E-2</v>
+      </c>
+      <c r="N23">
         <f t="shared" si="8"/>
-        <v>0.1077</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>0.17949999999999999</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="5"/>
-        <v>5.9234999999999996E-2</v>
-      </c>
-      <c r="N23">
-        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O23" s="5">
@@ -11267,25 +11253,25 @@
         <v>6</v>
       </c>
       <c r="I24">
+        <f t="shared" si="9"/>
+        <v>0.10829999999999999</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>0.18049999999999999</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="6"/>
+        <v>5.9565000000000007E-2</v>
+      </c>
+      <c r="N24">
         <f t="shared" si="8"/>
-        <v>0.10829999999999999</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="0"/>
-        <v>0.18049999999999999</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="5"/>
-        <v>5.9565000000000007E-2</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="7"/>
         <v>-5.9565000000000007E-2</v>
       </c>
       <c r="O24" s="5">
@@ -11321,25 +11307,25 @@
         <v>18</v>
       </c>
       <c r="I25">
+        <f t="shared" si="9"/>
+        <v>0.1077</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>0.17949999999999999</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="6"/>
+        <v>5.9234999999999996E-2</v>
+      </c>
+      <c r="N25">
         <f t="shared" si="8"/>
-        <v>0.1077</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="0"/>
-        <v>0.17949999999999999</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="5"/>
-        <v>5.9234999999999996E-2</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="7"/>
         <v>-5.9234999999999996E-2</v>
       </c>
       <c r="O25">
@@ -11369,25 +11355,25 @@
         <v>18</v>
       </c>
       <c r="I26">
+        <f t="shared" si="9"/>
+        <v>0.108</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="6"/>
+        <v>5.9400000000000008E-2</v>
+      </c>
+      <c r="N26">
         <f t="shared" si="8"/>
-        <v>0.108</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="0"/>
-        <v>0.18</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="5"/>
-        <v>5.9400000000000008E-2</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="7"/>
         <v>-5.9400000000000008E-2</v>
       </c>
       <c r="O26">
@@ -11417,25 +11403,25 @@
         <v>25</v>
       </c>
       <c r="I27">
+        <f t="shared" si="9"/>
+        <v>0.1278</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="6"/>
+        <v>7.0290000000000005E-2</v>
+      </c>
+      <c r="N27">
         <f t="shared" si="8"/>
-        <v>0.1278</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="0"/>
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="5"/>
-        <v>7.0290000000000005E-2</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O27">
@@ -11465,25 +11451,25 @@
         <v>25</v>
       </c>
       <c r="I28">
+        <f t="shared" si="9"/>
+        <v>0.1245</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>0.20749999999999999</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="6"/>
+        <v>6.8475000000000008E-2</v>
+      </c>
+      <c r="N28">
         <f t="shared" si="8"/>
-        <v>0.1245</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="0"/>
-        <v>0.20749999999999999</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="5"/>
-        <v>6.8475000000000008E-2</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O28">
@@ -11513,25 +11499,25 @@
         <v>13</v>
       </c>
       <c r="I29">
+        <f t="shared" si="9"/>
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="6"/>
+        <v>1.3695000000000001E-2</v>
+      </c>
+      <c r="N29">
         <f t="shared" si="8"/>
-        <v>2.4899999999999999E-2</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="0"/>
-        <v>4.1500000000000002E-2</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="5"/>
-        <v>1.3695000000000001E-2</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="7"/>
         <v>-1.3695000000000001E-2</v>
       </c>
       <c r="O29">
@@ -11561,25 +11547,25 @@
         <v>33</v>
       </c>
       <c r="I30">
+        <f t="shared" si="9"/>
+        <v>3.3600000000000005E-2</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="6"/>
+        <v>1.848E-2</v>
+      </c>
+      <c r="N30">
         <f t="shared" si="8"/>
-        <v>3.3600000000000005E-2</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="0"/>
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="5"/>
-        <v>1.848E-2</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="7"/>
         <v>-1.848E-2</v>
       </c>
       <c r="O30">
@@ -11609,25 +11595,25 @@
         <v>24</v>
       </c>
       <c r="I31">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999989E-3</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="6"/>
+        <v>3.96E-3</v>
+      </c>
+      <c r="N31">
         <f t="shared" si="8"/>
-        <v>7.1999999999999989E-3</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <f t="shared" si="5"/>
-        <v>3.96E-3</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O31">
@@ -11657,25 +11643,25 @@
         <v>24</v>
       </c>
       <c r="I32">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999989E-3</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="6"/>
+        <v>3.96E-3</v>
+      </c>
+      <c r="N32">
         <f t="shared" si="8"/>
-        <v>7.1999999999999989E-3</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <f t="shared" si="5"/>
-        <v>3.96E-3</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O32">
@@ -11705,25 +11691,25 @@
         <v>24</v>
       </c>
       <c r="I33">
+        <f t="shared" si="9"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>0.11</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="6"/>
+        <v>3.6300000000000006E-2</v>
+      </c>
+      <c r="N33">
         <f t="shared" si="8"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="0"/>
-        <v>0.11</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <f t="shared" si="5"/>
-        <v>3.6300000000000006E-2</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="7"/>
         <v>-3.6300000000000006E-2</v>
       </c>
       <c r="O33">
@@ -11753,25 +11739,25 @@
         <v>28</v>
       </c>
       <c r="I34">
+        <f t="shared" si="9"/>
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>3.95E-2</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="6"/>
+        <v>1.3035E-2</v>
+      </c>
+      <c r="N34">
         <f t="shared" si="8"/>
-        <v>2.3699999999999999E-2</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="0"/>
-        <v>3.95E-2</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="5"/>
-        <v>1.3035E-2</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="7"/>
         <v>-1.3035E-2</v>
       </c>
       <c r="O34">
@@ -11801,25 +11787,25 @@
         <v>11</v>
       </c>
       <c r="I35">
+        <f t="shared" si="9"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>0.2175</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="6"/>
+        <v>7.1775000000000005E-2</v>
+      </c>
+      <c r="N35">
         <f t="shared" si="8"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="0"/>
-        <v>0.2175</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="5"/>
-        <v>7.1775000000000005E-2</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O35">
@@ -11849,25 +11835,25 @@
         <v>11</v>
       </c>
       <c r="I36">
+        <f t="shared" si="9"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>0.2175</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="6"/>
+        <v>7.1775000000000005E-2</v>
+      </c>
+      <c r="N36">
         <f t="shared" si="8"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <f t="shared" si="0"/>
-        <v>0.2175</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <f t="shared" si="5"/>
-        <v>7.1775000000000005E-2</v>
-      </c>
-      <c r="N36">
-        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O36">
@@ -11897,25 +11883,25 @@
         <v>22</v>
       </c>
       <c r="I37">
+        <f t="shared" si="9"/>
+        <v>0.18</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="6"/>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="8"/>
-        <v>0.18</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <f t="shared" si="5"/>
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="7"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O37">
@@ -11945,25 +11931,25 @@
         <v>23</v>
       </c>
       <c r="I38">
+        <f t="shared" si="9"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>0.03</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="6"/>
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="N38">
         <f t="shared" si="8"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <f t="shared" si="0"/>
-        <v>0.03</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <f t="shared" si="5"/>
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="N38">
-        <f t="shared" si="7"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O38">
@@ -11993,25 +11979,25 @@
         <v>8</v>
       </c>
       <c r="I39">
+        <f t="shared" si="9"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>0.09</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="6"/>
+        <v>2.9700000000000004E-2</v>
+      </c>
+      <c r="N39">
         <f t="shared" si="8"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="0"/>
-        <v>0.09</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <f t="shared" si="5"/>
-        <v>2.9700000000000004E-2</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="7"/>
         <v>-2.9700000000000004E-2</v>
       </c>
       <c r="O39" s="5">
@@ -12047,25 +12033,25 @@
         <v>26</v>
       </c>
       <c r="I40">
+        <f t="shared" si="9"/>
+        <v>0.192</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>0.32</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="6"/>
+        <v>0.10560000000000001</v>
+      </c>
+      <c r="N40">
         <f t="shared" si="8"/>
-        <v>0.192</v>
-      </c>
-      <c r="J40">
-        <v>0</v>
-      </c>
-      <c r="K40">
-        <f t="shared" si="0"/>
-        <v>0.32</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <f t="shared" si="5"/>
-        <v>0.10560000000000001</v>
-      </c>
-      <c r="N40">
-        <f t="shared" si="7"/>
         <v>-0.10560000000000001</v>
       </c>
       <c r="O40">
@@ -12095,25 +12081,25 @@
         <v>26</v>
       </c>
       <c r="I41">
+        <f t="shared" si="9"/>
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>0.63749999999999996</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="6"/>
+        <v>0.21037500000000001</v>
+      </c>
+      <c r="N41">
         <f t="shared" si="8"/>
-        <v>0.38250000000000001</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41">
-        <f t="shared" si="0"/>
-        <v>0.63749999999999996</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <f t="shared" si="5"/>
-        <v>0.21037500000000001</v>
-      </c>
-      <c r="N41">
-        <f t="shared" si="7"/>
         <v>-0.21037500000000001</v>
       </c>
       <c r="O41">
@@ -12143,25 +12129,25 @@
         <v>8</v>
       </c>
       <c r="I42">
+        <f t="shared" si="9"/>
+        <v>0.105</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="6"/>
+        <v>5.7750000000000003E-2</v>
+      </c>
+      <c r="N42">
         <f t="shared" si="8"/>
-        <v>0.105</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <f t="shared" si="0"/>
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <f t="shared" si="5"/>
-        <v>5.7750000000000003E-2</v>
-      </c>
-      <c r="N42">
-        <f t="shared" si="7"/>
         <v>-5.7750000000000003E-2</v>
       </c>
       <c r="O42" s="5">
@@ -12197,25 +12183,25 @@
         <v>9</v>
       </c>
       <c r="I43">
+        <f t="shared" si="9"/>
+        <v>1.89E-2</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="1"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="6"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N43">
         <f t="shared" si="8"/>
-        <v>1.89E-2</v>
-      </c>
-      <c r="J43">
-        <v>0</v>
-      </c>
-      <c r="K43">
-        <f t="shared" si="0"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <f t="shared" si="5"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N43">
-        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O43" s="5">
@@ -12251,25 +12237,25 @@
         <v>9</v>
       </c>
       <c r="I44">
+        <f t="shared" si="9"/>
+        <v>1.89E-2</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="1"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="6"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N44">
         <f t="shared" si="8"/>
-        <v>1.89E-2</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <f t="shared" si="0"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <f t="shared" si="5"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N44">
-        <f t="shared" si="7"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O44" s="5">
@@ -12305,25 +12291,25 @@
         <v>26</v>
       </c>
       <c r="I45">
+        <f t="shared" si="9"/>
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="1"/>
+        <v>0.115</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="6"/>
+        <v>3.7950000000000005E-2</v>
+      </c>
+      <c r="N45">
         <f t="shared" si="8"/>
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <f t="shared" si="0"/>
-        <v>0.115</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="5"/>
-        <v>3.7950000000000005E-2</v>
-      </c>
-      <c r="N45">
-        <f t="shared" si="7"/>
         <v>-3.7950000000000005E-2</v>
       </c>
       <c r="O45">
@@ -12353,25 +12339,25 @@
         <v>30</v>
       </c>
       <c r="I46">
+        <f t="shared" si="9"/>
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="1"/>
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="6"/>
+        <v>5.4450000000000002E-3</v>
+      </c>
+      <c r="N46">
         <f t="shared" si="8"/>
-        <v>9.9000000000000008E-3</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <f t="shared" si="0"/>
-        <v>1.6500000000000001E-2</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <f t="shared" si="5"/>
-        <v>5.4450000000000002E-3</v>
-      </c>
-      <c r="N46">
-        <f t="shared" si="7"/>
         <v>-5.4450000000000002E-3</v>
       </c>
       <c r="O46">
@@ -12401,25 +12387,25 @@
         <v>16</v>
       </c>
       <c r="I47">
+        <f t="shared" si="9"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="6"/>
+        <v>4.1250000000000002E-3</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="8"/>
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <f t="shared" si="5"/>
-        <v>4.1250000000000002E-3</v>
-      </c>
-      <c r="N47">
-        <f t="shared" si="7"/>
         <v>-4.1250000000000002E-3</v>
       </c>
       <c r="O47">
@@ -12449,25 +12435,25 @@
         <v>22</v>
       </c>
       <c r="I48">
+        <f t="shared" si="9"/>
+        <v>9.5999999999999992E-3</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="1"/>
+        <v>1.6E-2</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="6"/>
+        <v>5.28E-3</v>
+      </c>
+      <c r="N48">
         <f t="shared" si="8"/>
-        <v>9.5999999999999992E-3</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
-      <c r="K48">
-        <f t="shared" si="0"/>
-        <v>1.6E-2</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <f t="shared" si="5"/>
-        <v>5.28E-3</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="7"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O48">
@@ -12497,25 +12483,25 @@
         <v>2</v>
       </c>
       <c r="I49">
+        <f t="shared" si="9"/>
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="1"/>
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="6"/>
+        <v>2.112E-2</v>
+      </c>
+      <c r="N49">
         <f t="shared" si="8"/>
-        <v>3.8399999999999997E-2</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <f t="shared" si="0"/>
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <f t="shared" si="5"/>
-        <v>2.112E-2</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="7"/>
         <v>-2.112E-2</v>
       </c>
       <c r="O49" s="5">
@@ -12551,25 +12537,25 @@
         <v>15</v>
       </c>
       <c r="I50">
+        <f t="shared" si="9"/>
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="1"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="6"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N50">
         <f t="shared" si="8"/>
-        <v>1.8599999999999998E-2</v>
-      </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50">
-        <f t="shared" si="0"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="5"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="7"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O50">
@@ -12599,25 +12585,25 @@
         <v>15</v>
       </c>
       <c r="I51">
+        <f t="shared" si="9"/>
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="1"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="6"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="8"/>
-        <v>1.6500000000000001E-2</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <f t="shared" si="0"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <f t="shared" si="5"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N51">
-        <f t="shared" si="7"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O51">
@@ -12647,25 +12633,25 @@
         <v>15</v>
       </c>
       <c r="I52">
+        <f t="shared" si="9"/>
+        <v>7.4700000000000003E-2</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="1"/>
+        <v>0.1245</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="6"/>
+        <v>4.1085000000000003E-2</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="8"/>
-        <v>7.4700000000000003E-2</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
-      </c>
-      <c r="K52">
-        <f t="shared" si="0"/>
-        <v>0.1245</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <f t="shared" si="5"/>
-        <v>4.1085000000000003E-2</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="7"/>
         <v>-4.1085000000000003E-2</v>
       </c>
       <c r="O52">
@@ -12695,25 +12681,25 @@
         <v>12</v>
       </c>
       <c r="I53">
+        <f t="shared" si="9"/>
+        <v>4.3199999999999995E-2</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="1"/>
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="6"/>
+        <v>2.376E-2</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="8"/>
-        <v>4.3199999999999995E-2</v>
-      </c>
-      <c r="J53">
-        <v>0</v>
-      </c>
-      <c r="K53">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999995E-2</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <f t="shared" si="5"/>
-        <v>2.376E-2</v>
-      </c>
-      <c r="N53">
-        <f t="shared" si="7"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O53">
@@ -12743,25 +12729,25 @@
         <v>10</v>
       </c>
       <c r="I54">
+        <f t="shared" si="9"/>
+        <v>7.4399999999999994E-2</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="1"/>
+        <v>0.124</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="6"/>
+        <v>4.0920000000000005E-2</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="8"/>
-        <v>7.4399999999999994E-2</v>
-      </c>
-      <c r="J54">
-        <v>0</v>
-      </c>
-      <c r="K54">
-        <f t="shared" si="0"/>
-        <v>0.124</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <f t="shared" si="5"/>
-        <v>4.0920000000000005E-2</v>
-      </c>
-      <c r="N54">
-        <f t="shared" si="7"/>
         <v>-4.0920000000000005E-2</v>
       </c>
       <c r="O54">
@@ -12791,25 +12777,25 @@
         <v>10</v>
       </c>
       <c r="I55">
+        <f t="shared" si="9"/>
+        <v>3.0899999999999997E-2</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="1"/>
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="6"/>
+        <v>1.6995E-2</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="8"/>
-        <v>3.0899999999999997E-2</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <f t="shared" si="0"/>
-        <v>5.1499999999999997E-2</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <f t="shared" si="5"/>
-        <v>1.6995E-2</v>
-      </c>
-      <c r="N55">
-        <f t="shared" si="7"/>
         <v>-1.6995E-2</v>
       </c>
       <c r="O55">
@@ -12839,25 +12825,25 @@
         <v>10</v>
       </c>
       <c r="I56">
+        <f t="shared" si="9"/>
+        <v>6.7500000000000004E-2</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="1"/>
+        <v>0.1125</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="6"/>
+        <v>3.7124999999999998E-2</v>
+      </c>
+      <c r="N56">
         <f t="shared" si="8"/>
-        <v>6.7500000000000004E-2</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <f t="shared" si="0"/>
-        <v>0.1125</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <f t="shared" si="5"/>
-        <v>3.7124999999999998E-2</v>
-      </c>
-      <c r="N56">
-        <f t="shared" si="7"/>
         <v>-3.7124999999999998E-2</v>
       </c>
       <c r="O56">
@@ -12887,25 +12873,25 @@
         <v>15</v>
       </c>
       <c r="I57">
+        <f t="shared" si="9"/>
+        <v>2.0099999999999996E-2</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <f t="shared" si="1"/>
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="6"/>
+        <v>1.1054999999999999E-2</v>
+      </c>
+      <c r="N57">
         <f t="shared" si="8"/>
-        <v>2.0099999999999996E-2</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
-      <c r="K57">
-        <f t="shared" si="0"/>
-        <v>3.3500000000000002E-2</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <f t="shared" si="5"/>
-        <v>1.1054999999999999E-2</v>
-      </c>
-      <c r="N57">
-        <f t="shared" si="7"/>
         <v>-1.1054999999999999E-2</v>
       </c>
       <c r="O57">
@@ -12935,25 +12921,25 @@
         <v>12</v>
       </c>
       <c r="I58">
+        <f t="shared" si="9"/>
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <f t="shared" si="1"/>
+        <v>0.23</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="6"/>
+        <v>7.5900000000000009E-2</v>
+      </c>
+      <c r="N58">
         <f t="shared" si="8"/>
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="J58">
-        <v>0</v>
-      </c>
-      <c r="K58">
-        <f t="shared" si="0"/>
-        <v>0.23</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <f t="shared" si="5"/>
-        <v>7.5900000000000009E-2</v>
-      </c>
-      <c r="N58">
-        <f t="shared" si="7"/>
         <v>-7.5900000000000009E-2</v>
       </c>
       <c r="O58">
@@ -12983,25 +12969,25 @@
         <v>12</v>
       </c>
       <c r="I59">
+        <f t="shared" si="9"/>
+        <v>0.114</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="1"/>
+        <v>0.19</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="6"/>
+        <v>6.2700000000000006E-2</v>
+      </c>
+      <c r="N59">
         <f t="shared" si="8"/>
-        <v>0.114</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <f t="shared" si="0"/>
-        <v>0.19</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <f t="shared" si="5"/>
-        <v>6.2700000000000006E-2</v>
-      </c>
-      <c r="N59">
-        <f t="shared" si="7"/>
         <v>-6.2700000000000006E-2</v>
       </c>
       <c r="O59">
@@ -13031,25 +13017,25 @@
         <v>29</v>
       </c>
       <c r="I60">
+        <f t="shared" si="9"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <f t="shared" si="1"/>
+        <v>0.22</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="6"/>
+        <v>7.2600000000000012E-2</v>
+      </c>
+      <c r="N60">
         <f t="shared" si="8"/>
-        <v>0.13200000000000001</v>
-      </c>
-      <c r="J60">
-        <v>0</v>
-      </c>
-      <c r="K60">
-        <f t="shared" si="0"/>
-        <v>0.22</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <f t="shared" si="5"/>
-        <v>7.2600000000000012E-2</v>
-      </c>
-      <c r="N60">
-        <f t="shared" si="7"/>
         <v>-7.2600000000000012E-2</v>
       </c>
       <c r="O60">
@@ -13079,25 +13065,25 @@
         <v>28</v>
       </c>
       <c r="I61">
+        <f t="shared" si="9"/>
+        <v>0.1278</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="1"/>
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="6"/>
+        <v>7.0290000000000005E-2</v>
+      </c>
+      <c r="N61">
         <f t="shared" si="8"/>
-        <v>0.1278</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <f t="shared" si="0"/>
-        <v>0.21299999999999999</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <f t="shared" si="5"/>
-        <v>7.0290000000000005E-2</v>
-      </c>
-      <c r="N61">
-        <f t="shared" si="7"/>
         <v>-7.0290000000000005E-2</v>
       </c>
       <c r="O61">
@@ -13127,25 +13113,25 @@
         <v>22</v>
       </c>
       <c r="I62">
+        <f t="shared" si="9"/>
+        <v>0.10529999999999999</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="1"/>
+        <v>0.17549999999999999</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="6"/>
+        <v>5.7915000000000008E-2</v>
+      </c>
+      <c r="N62">
         <f t="shared" si="8"/>
-        <v>0.10529999999999999</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <f t="shared" si="0"/>
-        <v>0.17549999999999999</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <f t="shared" si="5"/>
-        <v>5.7915000000000008E-2</v>
-      </c>
-      <c r="N62">
-        <f t="shared" si="7"/>
         <v>-5.7915000000000008E-2</v>
       </c>
       <c r="O62">
@@ -13175,25 +13161,25 @@
         <v>22</v>
       </c>
       <c r="I63">
+        <f t="shared" si="9"/>
+        <v>0.1245</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="1"/>
+        <v>0.20749999999999999</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="6"/>
+        <v>6.8475000000000008E-2</v>
+      </c>
+      <c r="N63">
         <f t="shared" si="8"/>
-        <v>0.1245</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <f t="shared" si="0"/>
-        <v>0.20749999999999999</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <f t="shared" si="5"/>
-        <v>6.8475000000000008E-2</v>
-      </c>
-      <c r="N63">
-        <f t="shared" si="7"/>
         <v>-6.8475000000000008E-2</v>
       </c>
       <c r="O63">
@@ -13223,25 +13209,25 @@
         <v>30</v>
       </c>
       <c r="I64">
+        <f t="shared" si="9"/>
+        <v>7.1999999999999989E-3</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="1"/>
+        <v>1.2E-2</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="6"/>
+        <v>3.96E-3</v>
+      </c>
+      <c r="N64">
         <f t="shared" si="8"/>
-        <v>7.1999999999999989E-3</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <f t="shared" si="0"/>
-        <v>1.2E-2</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <f t="shared" si="5"/>
-        <v>3.96E-3</v>
-      </c>
-      <c r="N64">
-        <f t="shared" si="7"/>
         <v>-3.96E-3</v>
       </c>
       <c r="O64">
@@ -13271,25 +13257,25 @@
         <v>21</v>
       </c>
       <c r="I65">
+        <f t="shared" si="9"/>
+        <v>0.13109999999999999</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="1"/>
+        <v>0.2185</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="6"/>
+        <v>7.2105000000000002E-2</v>
+      </c>
+      <c r="N65">
         <f t="shared" si="8"/>
-        <v>0.13109999999999999</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <f t="shared" si="0"/>
-        <v>0.2185</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <f t="shared" si="5"/>
-        <v>7.2105000000000002E-2</v>
-      </c>
-      <c r="N65">
-        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O65">
@@ -13319,25 +13305,25 @@
         <v>21</v>
       </c>
       <c r="I66">
+        <f t="shared" si="9"/>
+        <v>0.13109999999999999</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="1"/>
+        <v>0.2185</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <f t="shared" si="6"/>
+        <v>7.2105000000000002E-2</v>
+      </c>
+      <c r="N66">
         <f t="shared" si="8"/>
-        <v>0.13109999999999999</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <f t="shared" si="0"/>
-        <v>0.2185</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <f t="shared" si="5"/>
-        <v>7.2105000000000002E-2</v>
-      </c>
-      <c r="N66">
-        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O66">
@@ -13367,25 +13353,25 @@
         <v>21</v>
       </c>
       <c r="I67">
+        <f t="shared" si="9"/>
+        <v>0.13109999999999999</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K130" si="10">E67/2000</f>
+        <v>0.2185</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="6"/>
+        <v>7.2105000000000002E-2</v>
+      </c>
+      <c r="N67">
         <f t="shared" si="8"/>
-        <v>0.13109999999999999</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <f t="shared" ref="K67:K130" si="9">E67/2000</f>
-        <v>0.2185</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <f t="shared" si="5"/>
-        <v>7.2105000000000002E-2</v>
-      </c>
-      <c r="N67">
-        <f t="shared" si="7"/>
         <v>-7.2105000000000002E-2</v>
       </c>
       <c r="O67">
@@ -13415,25 +13401,25 @@
         <v>15</v>
       </c>
       <c r="I68">
+        <f t="shared" si="9"/>
+        <v>0.1305</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="10"/>
+        <v>0.2175</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="6"/>
+        <v>7.1775000000000005E-2</v>
+      </c>
+      <c r="N68">
         <f t="shared" si="8"/>
-        <v>0.1305</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <f t="shared" si="9"/>
-        <v>0.2175</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <f t="shared" si="5"/>
-        <v>7.1775000000000005E-2</v>
-      </c>
-      <c r="N68">
-        <f t="shared" si="7"/>
         <v>-7.1775000000000005E-2</v>
       </c>
       <c r="O68">
@@ -13463,25 +13449,25 @@
         <v>22</v>
       </c>
       <c r="I69">
+        <f t="shared" si="9"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="10"/>
+        <v>0.06</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="6"/>
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="N69">
         <f t="shared" si="8"/>
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <f t="shared" si="9"/>
-        <v>0.06</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <f t="shared" si="5"/>
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="N69">
-        <f t="shared" si="7"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O69">
@@ -13511,25 +13497,25 @@
         <v>22</v>
       </c>
       <c r="I70">
+        <f t="shared" si="9"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="10"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="6"/>
+        <v>5.94E-3</v>
+      </c>
+      <c r="N70">
         <f t="shared" si="8"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <f t="shared" si="9"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <f t="shared" si="5"/>
-        <v>5.94E-3</v>
-      </c>
-      <c r="N70">
-        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O70">
@@ -13559,25 +13545,25 @@
         <v>23</v>
       </c>
       <c r="I71">
+        <f t="shared" si="9"/>
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="10"/>
+        <v>1.15E-2</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="6"/>
+        <v>3.7950000000000002E-3</v>
+      </c>
+      <c r="N71">
         <f t="shared" si="8"/>
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <f t="shared" si="9"/>
-        <v>1.15E-2</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <f t="shared" si="5"/>
-        <v>3.7950000000000002E-3</v>
-      </c>
-      <c r="N71">
-        <f t="shared" si="7"/>
         <v>-3.7950000000000002E-3</v>
       </c>
       <c r="O71">
@@ -13607,25 +13593,25 @@
         <v>8</v>
       </c>
       <c r="I72">
+        <f t="shared" si="9"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="10"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="6"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N72">
         <f t="shared" si="8"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <f t="shared" si="5"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N72">
-        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O72" s="5">
@@ -13661,25 +13647,25 @@
         <v>51</v>
       </c>
       <c r="I73">
+        <f t="shared" si="9"/>
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="10"/>
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="6"/>
+        <v>2.0130000000000002E-2</v>
+      </c>
+      <c r="N73">
         <f t="shared" si="8"/>
-        <v>3.6600000000000001E-2</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <f t="shared" si="9"/>
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <f t="shared" si="5"/>
-        <v>2.0130000000000002E-2</v>
-      </c>
-      <c r="N73">
-        <f t="shared" si="7"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O73">
@@ -13709,25 +13695,25 @@
         <v>17</v>
       </c>
       <c r="I74">
+        <f t="shared" si="9"/>
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="10"/>
+        <v>1.55E-2</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="6"/>
+        <v>5.1150000000000006E-3</v>
+      </c>
+      <c r="N74">
         <f t="shared" si="8"/>
-        <v>9.2999999999999992E-3</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <f t="shared" si="9"/>
-        <v>1.55E-2</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <f t="shared" si="5"/>
-        <v>5.1150000000000006E-3</v>
-      </c>
-      <c r="N74">
-        <f t="shared" si="7"/>
         <v>-5.1150000000000006E-3</v>
       </c>
       <c r="O74">
@@ -13757,25 +13743,25 @@
         <v>23</v>
       </c>
       <c r="I75">
+        <f t="shared" si="9"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="10"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="6"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N75">
         <f t="shared" si="8"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <f t="shared" si="5"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N75">
-        <f t="shared" si="7"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O75">
@@ -13805,25 +13791,25 @@
         <v>8</v>
       </c>
       <c r="I76">
+        <f t="shared" si="9"/>
+        <v>1.0799999999999999E-2</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="10"/>
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <f t="shared" ref="M76:M139" si="11">0.33*E76/2000</f>
+        <v>5.94E-3</v>
+      </c>
+      <c r="N76">
         <f t="shared" si="8"/>
-        <v>1.0799999999999999E-2</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <f t="shared" si="9"/>
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <f t="shared" ref="M76:M139" si="10">0.33*E76/2000</f>
-        <v>5.94E-3</v>
-      </c>
-      <c r="N76">
-        <f t="shared" si="7"/>
         <v>-5.94E-3</v>
       </c>
       <c r="O76" s="5">
@@ -13859,25 +13845,25 @@
         <v>12</v>
       </c>
       <c r="I77">
+        <f t="shared" si="9"/>
+        <v>1.95E-2</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="10"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="11"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N77">
         <f t="shared" si="8"/>
-        <v>1.95E-2</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <f t="shared" si="9"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <f t="shared" si="10"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N77">
-        <f t="shared" si="7"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O77">
@@ -13907,25 +13893,25 @@
         <v>14</v>
       </c>
       <c r="I78">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6E-2</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.28E-3</v>
       </c>
       <c r="N78">
-        <f t="shared" ref="N78:N139" si="11">-M78</f>
+        <f t="shared" ref="N78:N139" si="12">-M78</f>
         <v>-5.28E-3</v>
       </c>
       <c r="O78">
@@ -13955,25 +13941,25 @@
         <v>29</v>
       </c>
       <c r="I79">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.4750000000000001E-2</v>
       </c>
       <c r="N79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.4750000000000001E-2</v>
       </c>
       <c r="O79">
@@ -14003,25 +13989,25 @@
         <v>51</v>
       </c>
       <c r="I80">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.03</v>
       </c>
       <c r="L80">
         <v>0</v>
       </c>
       <c r="M80">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N80">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.9000000000000008E-3</v>
       </c>
       <c r="O80">
@@ -14051,25 +14037,25 @@
         <v>50</v>
       </c>
       <c r="I81">
-        <f t="shared" ref="I81:I82" si="12">0.6*E81/2000</f>
+        <f t="shared" ref="I81:I82" si="13">0.6*E81/2000</f>
         <v>9.5999999999999992E-3</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6E-2</v>
       </c>
       <c r="L81">
         <v>0</v>
       </c>
       <c r="M81">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.28E-3</v>
       </c>
       <c r="N81">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5.28E-3</v>
       </c>
       <c r="O81">
@@ -14100,25 +14086,25 @@
       </c>
       <c r="H82" s="10"/>
       <c r="I82">
+        <f t="shared" si="13"/>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="10"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L82" s="10">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="11"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N82">
         <f t="shared" si="12"/>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <f t="shared" si="9"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L82" s="10">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <f t="shared" si="10"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N82">
-        <f t="shared" si="11"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O82" s="10">
@@ -14159,18 +14145,18 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="L83">
         <v>0</v>
       </c>
       <c r="M83">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="N83">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.9000000000000005E-2</v>
       </c>
       <c r="O83">
@@ -14200,25 +14186,25 @@
         <v>13</v>
       </c>
       <c r="I84" s="27">
-        <f t="shared" ref="I84:I109" si="13">0.35*K84</f>
+        <f t="shared" ref="I84:I109" si="14">0.35*K84</f>
         <v>2.2574999999999998E-2</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.4500000000000002E-2</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
       <c r="M84">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.1285000000000002E-2</v>
       </c>
       <c r="N84">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.1285000000000002E-2</v>
       </c>
       <c r="O84">
@@ -14248,25 +14234,25 @@
         <v>12</v>
       </c>
       <c r="I85" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.0999999999999998E-2</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.06</v>
       </c>
       <c r="L85">
         <v>0</v>
       </c>
       <c r="M85">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="N85">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.9800000000000002E-2</v>
       </c>
       <c r="O85">
@@ -14296,25 +14282,25 @@
         <v>12</v>
       </c>
       <c r="I86" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.89E-2</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="L86">
         <v>0</v>
       </c>
       <c r="M86">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7819999999999999E-2</v>
       </c>
       <c r="N86">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O86">
@@ -14344,25 +14330,25 @@
         <v>15</v>
       </c>
       <c r="I87" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.1349999999999997E-2</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.0130000000000002E-2</v>
       </c>
       <c r="N87">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.0130000000000002E-2</v>
       </c>
       <c r="O87">
@@ -14392,25 +14378,25 @@
         <v>6</v>
       </c>
       <c r="I88" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.9925E-2</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.5500000000000007E-2</v>
       </c>
       <c r="L88">
         <v>0</v>
       </c>
       <c r="M88">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.8215E-2</v>
       </c>
       <c r="N88">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.8215E-2</v>
       </c>
       <c r="O88" s="5">
@@ -14446,25 +14432,25 @@
         <v>5</v>
       </c>
       <c r="I89" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.5199999999999997E-2</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.1999999999999995E-2</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.376E-2</v>
       </c>
       <c r="N89">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.376E-2</v>
       </c>
       <c r="O89" s="5">
@@ -14500,25 +14486,25 @@
         <v>5</v>
       </c>
       <c r="I90" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.9874999999999996E-2</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14249999999999999</v>
       </c>
       <c r="L90">
         <v>0</v>
       </c>
       <c r="M90">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.7025000000000004E-2</v>
       </c>
       <c r="N90">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.7025000000000004E-2</v>
       </c>
       <c r="O90" s="5">
@@ -14554,25 +14540,25 @@
         <v>28</v>
       </c>
       <c r="I91" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.7849999999999998E-2</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6830000000000001E-2</v>
       </c>
       <c r="N91">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O91">
@@ -14602,25 +14588,25 @@
         <v>30</v>
       </c>
       <c r="I92" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.4437499999999999E-2</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.1250000000000002E-2</v>
       </c>
       <c r="L92">
         <v>0</v>
       </c>
       <c r="M92">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3612500000000001E-2</v>
       </c>
       <c r="N92">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.3612500000000001E-2</v>
       </c>
       <c r="O92">
@@ -14650,25 +14636,25 @@
         <v>8</v>
       </c>
       <c r="I93" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.09725E-2</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.1350000000000003E-2</v>
       </c>
       <c r="L93">
         <v>0</v>
       </c>
       <c r="M93">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0345500000000001E-2</v>
       </c>
       <c r="N93">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.0345500000000001E-2</v>
       </c>
       <c r="O93" s="5">
@@ -14704,25 +14690,25 @@
         <v>28</v>
       </c>
       <c r="I94" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.8199999999999997E-3</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.52E-2</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="M94">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.3160000000000005E-3</v>
       </c>
       <c r="N94">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8.3160000000000005E-3</v>
       </c>
       <c r="O94">
@@ -14752,25 +14738,25 @@
         <v>29</v>
       </c>
       <c r="I95" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.5299999999999995E-2</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.158</v>
       </c>
       <c r="L95">
         <v>0</v>
       </c>
       <c r="M95">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.2139999999999999E-2</v>
       </c>
       <c r="N95">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-5.2139999999999999E-2</v>
       </c>
       <c r="O95">
@@ -14800,25 +14786,25 @@
         <v>4</v>
       </c>
       <c r="I96" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.47E-2</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="L96">
         <v>0</v>
       </c>
       <c r="M96">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.3860000000000001E-2</v>
       </c>
       <c r="N96">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.3860000000000001E-2</v>
       </c>
       <c r="O96" s="5">
@@ -14854,25 +14840,25 @@
         <v>4</v>
       </c>
       <c r="I97" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.1025E-2</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.15E-2</v>
       </c>
       <c r="L97">
         <v>0</v>
       </c>
       <c r="M97">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0395000000000001E-2</v>
       </c>
       <c r="N97">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O97" s="5">
@@ -14908,25 +14894,25 @@
         <v>29</v>
       </c>
       <c r="I98" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.13685</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.39100000000000001</v>
       </c>
       <c r="L98">
         <v>0</v>
       </c>
       <c r="M98">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12903000000000001</v>
       </c>
       <c r="N98">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12903000000000001</v>
       </c>
       <c r="O98">
@@ -14956,25 +14942,25 @@
         <v>32</v>
       </c>
       <c r="I99" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.14402499999999999</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.41149999999999998</v>
       </c>
       <c r="L99">
         <v>0</v>
       </c>
       <c r="M99">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.13579500000000003</v>
       </c>
       <c r="N99">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.13579500000000003</v>
       </c>
       <c r="O99">
@@ -15004,25 +14990,25 @@
         <v>11</v>
       </c>
       <c r="I100" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.117075</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.33450000000000002</v>
       </c>
       <c r="L100">
         <v>0</v>
       </c>
       <c r="M100">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.11038500000000001</v>
       </c>
       <c r="N100">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.11038500000000001</v>
       </c>
       <c r="O100">
@@ -15052,25 +15038,25 @@
         <v>25</v>
       </c>
       <c r="I101" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.41475000000000001</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.1850000000000001</v>
       </c>
       <c r="L101">
         <v>0</v>
       </c>
       <c r="M101">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.39105000000000001</v>
       </c>
       <c r="N101">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.39105000000000001</v>
       </c>
       <c r="O101">
@@ -15100,25 +15086,25 @@
         <v>17</v>
       </c>
       <c r="I102" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.7425000000000002E-2</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.13550000000000001</v>
       </c>
       <c r="L102">
         <v>0</v>
       </c>
       <c r="M102">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.4715000000000005E-2</v>
       </c>
       <c r="N102">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.4715000000000005E-2</v>
       </c>
       <c r="O102">
@@ -15148,25 +15134,25 @@
         <v>6</v>
       </c>
       <c r="I103" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.17587499999999998</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.50249999999999995</v>
       </c>
       <c r="L103">
         <v>0</v>
       </c>
       <c r="M103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.16582500000000003</v>
       </c>
       <c r="N103">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.16582500000000003</v>
       </c>
       <c r="O103" s="5">
@@ -15202,25 +15188,25 @@
         <v>3</v>
       </c>
       <c r="I104" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.118475</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.33850000000000002</v>
       </c>
       <c r="L104">
         <v>0</v>
       </c>
       <c r="M104">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.111705</v>
       </c>
       <c r="N104">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.111705</v>
       </c>
       <c r="O104" s="5">
@@ -15256,25 +15242,25 @@
         <v>9</v>
       </c>
       <c r="I105" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.1974999999999993E-2</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.14849999999999999</v>
       </c>
       <c r="L105">
         <v>0</v>
       </c>
       <c r="M105">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4.9005E-2</v>
       </c>
       <c r="N105">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4.9005E-2</v>
       </c>
       <c r="O105" s="5">
@@ -15310,25 +15296,25 @@
         <v>34</v>
       </c>
       <c r="I106" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.6624999999999997E-2</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.7500000000000001E-2</v>
       </c>
       <c r="L106">
         <v>0</v>
       </c>
       <c r="M106">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5675000000000001E-2</v>
       </c>
       <c r="N106">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.5675000000000001E-2</v>
       </c>
       <c r="O106">
@@ -15358,25 +15344,25 @@
         <v>26</v>
       </c>
       <c r="I107" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.3975E-2</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="L107">
         <v>0</v>
       </c>
       <c r="M107">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.2605E-2</v>
       </c>
       <c r="N107">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.2605E-2</v>
       </c>
       <c r="O107">
@@ -15406,25 +15392,25 @@
         <v>22</v>
       </c>
       <c r="I108" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.1375000000000003E-2</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.23250000000000001</v>
       </c>
       <c r="L108">
         <v>0</v>
       </c>
       <c r="M108">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7.6725000000000015E-2</v>
       </c>
       <c r="N108">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7.6725000000000015E-2</v>
       </c>
       <c r="O108">
@@ -15454,25 +15440,25 @@
         <v>10</v>
       </c>
       <c r="I109" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.474999999999999E-3</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8499999999999999E-2</v>
       </c>
       <c r="L109">
         <v>0</v>
       </c>
       <c r="M109">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6.1050000000000002E-3</v>
       </c>
       <c r="N109">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6.1050000000000002E-3</v>
       </c>
       <c r="O109">
@@ -15509,18 +15495,18 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.5E-2</v>
       </c>
       <c r="L110">
         <v>0</v>
       </c>
       <c r="M110">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.8150000000000003E-2</v>
       </c>
       <c r="N110">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.8150000000000003E-2</v>
       </c>
       <c r="O110" s="5">
@@ -15556,25 +15542,25 @@
         <v>4</v>
       </c>
       <c r="I111" s="28">
-        <f t="shared" ref="I111:I125" si="14">0.1*K111</f>
+        <f t="shared" ref="I111:I125" si="15">0.1*K111</f>
         <v>5.1000000000000004E-3</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="L111">
         <v>0</v>
       </c>
       <c r="M111">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.6830000000000001E-2</v>
       </c>
       <c r="N111">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.6830000000000001E-2</v>
       </c>
       <c r="O111" s="5">
@@ -15610,25 +15596,25 @@
         <v>4</v>
       </c>
       <c r="I112" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="L112">
         <v>0</v>
       </c>
       <c r="M112">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.056E-2</v>
       </c>
       <c r="N112">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.056E-2</v>
       </c>
       <c r="O112" s="5">
@@ -15664,25 +15650,25 @@
         <v>11</v>
       </c>
       <c r="I113" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.725E-3</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.725E-2</v>
       </c>
       <c r="L113">
         <v>0</v>
       </c>
       <c r="M113">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.9925000000000005E-3</v>
       </c>
       <c r="N113">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-8.9925000000000005E-3</v>
       </c>
       <c r="O113">
@@ -15712,25 +15698,25 @@
         <v>29</v>
       </c>
       <c r="I114" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.36099999999999999</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.61</v>
       </c>
       <c r="L114">
         <v>0</v>
       </c>
       <c r="M114">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.1913</v>
       </c>
       <c r="N114">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.1913</v>
       </c>
       <c r="O114">
@@ -15760,25 +15746,25 @@
         <v>32</v>
       </c>
       <c r="I115" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.46445000000000003</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6444999999999999</v>
       </c>
       <c r="L115">
         <v>0</v>
       </c>
       <c r="M115">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.5326850000000001</v>
       </c>
       <c r="N115">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.5326850000000001</v>
       </c>
       <c r="O115">
@@ -15808,25 +15794,25 @@
         <v>11</v>
       </c>
       <c r="I116" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.15329999999999999</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.5329999999999999</v>
       </c>
       <c r="L116">
         <v>0</v>
       </c>
       <c r="M116">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.50589000000000006</v>
       </c>
       <c r="N116">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.50589000000000006</v>
       </c>
       <c r="O116">
@@ -15856,25 +15842,25 @@
         <v>25</v>
       </c>
       <c r="I117" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.17660000000000001</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.766</v>
       </c>
       <c r="L117">
         <v>0</v>
       </c>
       <c r="M117">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.58277999999999996</v>
       </c>
       <c r="N117">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.58277999999999996</v>
       </c>
       <c r="O117">
@@ -15904,25 +15890,25 @@
         <v>17</v>
       </c>
       <c r="I118" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.52739999999999998</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.274</v>
       </c>
       <c r="L118">
         <v>0</v>
       </c>
       <c r="M118">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.7404200000000001</v>
       </c>
       <c r="N118">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.7404200000000001</v>
       </c>
       <c r="O118">
@@ -15952,25 +15938,25 @@
         <v>6</v>
       </c>
       <c r="I119" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.25714999999999999</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5714999999999999</v>
       </c>
       <c r="L119">
         <v>0</v>
       </c>
       <c r="M119">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.84859499999999999</v>
       </c>
       <c r="N119">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.84859499999999999</v>
       </c>
       <c r="O119" s="5">
@@ -16006,25 +15992,25 @@
         <v>3</v>
       </c>
       <c r="I120" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.19595000000000001</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.9595</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="M120">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.64663499999999996</v>
       </c>
       <c r="N120">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.64663499999999996</v>
       </c>
       <c r="O120" s="5">
@@ -16060,25 +16046,25 @@
         <v>9</v>
       </c>
       <c r="I121" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.25445000000000001</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5445000000000002</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="M121">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.83968500000000001</v>
       </c>
       <c r="N121">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.83968500000000001</v>
       </c>
       <c r="O121" s="5">
@@ -16114,25 +16100,25 @@
         <v>34</v>
       </c>
       <c r="I122" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.31505000000000005</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.1505000000000001</v>
       </c>
       <c r="L122">
         <v>0</v>
       </c>
       <c r="M122">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0396650000000001</v>
       </c>
       <c r="N122">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1.0396650000000001</v>
       </c>
       <c r="O122">
@@ -16162,25 +16148,25 @@
         <v>26</v>
       </c>
       <c r="I123" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.29694999999999999</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.9695</v>
       </c>
       <c r="L123">
         <v>0</v>
       </c>
       <c r="M123">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.97993500000000011</v>
       </c>
       <c r="N123">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.97993500000000011</v>
       </c>
       <c r="O123">
@@ -16210,25 +16196,25 @@
         <v>22</v>
       </c>
       <c r="I124" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.65195000000000003</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.5194999999999999</v>
       </c>
       <c r="L124">
         <v>0</v>
       </c>
       <c r="M124">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2.1514349999999998</v>
       </c>
       <c r="N124">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2.1514349999999998</v>
       </c>
       <c r="O124">
@@ -16258,25 +16244,25 @@
         <v>10</v>
       </c>
       <c r="I125" s="28">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.21299999999999999</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.13</v>
       </c>
       <c r="L125">
         <v>0</v>
       </c>
       <c r="M125">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.70289999999999997</v>
       </c>
       <c r="N125">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.70289999999999997</v>
       </c>
       <c r="O125">
@@ -16313,18 +16299,18 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="L126">
         <v>0</v>
       </c>
       <c r="M126">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12540000000000001</v>
       </c>
       <c r="N126">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O126">
@@ -16354,25 +16340,25 @@
         <v>28</v>
       </c>
       <c r="I127" s="27">
-        <f t="shared" ref="I127:I143" si="15">0.35*K127</f>
+        <f t="shared" ref="I127:I143" si="16">0.35*K127</f>
         <v>0.13299999999999998</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.38</v>
       </c>
       <c r="L127">
         <v>0</v>
       </c>
       <c r="M127">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12540000000000001</v>
       </c>
       <c r="N127">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12540000000000001</v>
       </c>
       <c r="O127">
@@ -16402,25 +16388,25 @@
         <v>12</v>
       </c>
       <c r="I128" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.132825</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.3795</v>
       </c>
       <c r="L128">
         <v>0</v>
       </c>
       <c r="M128">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12523500000000001</v>
       </c>
       <c r="N128">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12523500000000001</v>
       </c>
       <c r="O128">
@@ -16450,25 +16436,25 @@
         <v>12</v>
       </c>
       <c r="I129" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.1323</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.378</v>
       </c>
       <c r="L129">
         <v>0</v>
       </c>
       <c r="M129">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12474</v>
       </c>
       <c r="N129">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12474</v>
       </c>
       <c r="O129">
@@ -16498,25 +16484,25 @@
         <v>12</v>
       </c>
       <c r="I130" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.12249999999999998</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
       <c r="L130">
         <v>0</v>
       </c>
       <c r="M130">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.11550000000000001</v>
       </c>
       <c r="N130">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.11550000000000001</v>
       </c>
       <c r="O130">
@@ -16546,25 +16532,25 @@
         <v>12</v>
       </c>
       <c r="I131" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.10149999999999999</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <f t="shared" ref="K131:K171" si="16">E131/2000</f>
+        <f t="shared" ref="K131:K171" si="17">E131/2000</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="L131">
         <v>0</v>
       </c>
       <c r="M131">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>9.5700000000000007E-2</v>
       </c>
       <c r="N131">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9.5700000000000007E-2</v>
       </c>
       <c r="O131">
@@ -16594,25 +16580,25 @@
         <v>11</v>
       </c>
       <c r="I132" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.13159999999999999</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
       <c r="K132">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.376</v>
       </c>
       <c r="L132">
         <v>0</v>
       </c>
       <c r="M132">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.12408000000000001</v>
       </c>
       <c r="N132">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.12408000000000001</v>
       </c>
       <c r="O132">
@@ -16642,25 +16628,25 @@
         <v>11</v>
       </c>
       <c r="I133" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.1280125</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.36575000000000002</v>
       </c>
       <c r="L133">
         <v>0</v>
       </c>
       <c r="M133">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.1206975</v>
       </c>
       <c r="N133">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.1206975</v>
       </c>
       <c r="O133">
@@ -16690,25 +16676,25 @@
         <v>11</v>
       </c>
       <c r="I134" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>3.3249999999999998E-3</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.4999999999999998E-3</v>
       </c>
       <c r="L134">
         <v>0</v>
       </c>
       <c r="M134">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.1350000000000002E-3</v>
       </c>
       <c r="N134">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3.1350000000000002E-3</v>
       </c>
       <c r="O134">
@@ -16738,25 +16724,25 @@
         <v>28</v>
       </c>
       <c r="I135" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.35</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L135">
         <v>0</v>
       </c>
       <c r="M135">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33</v>
       </c>
       <c r="N135">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O135">
@@ -16786,25 +16772,25 @@
         <v>11</v>
       </c>
       <c r="I136" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.35</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L136">
         <v>0</v>
       </c>
       <c r="M136">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33</v>
       </c>
       <c r="N136">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O136">
@@ -16834,25 +16820,25 @@
         <v>28</v>
       </c>
       <c r="I137" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.35</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L137">
         <v>0</v>
       </c>
       <c r="M137">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.33</v>
       </c>
       <c r="N137">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.33</v>
       </c>
       <c r="O137">
@@ -16882,25 +16868,25 @@
         <v>22</v>
       </c>
       <c r="I138" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.52499999999999991</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="L138">
         <v>0</v>
       </c>
       <c r="M138">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.495</v>
       </c>
       <c r="N138">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O138">
@@ -16930,25 +16916,25 @@
         <v>22</v>
       </c>
       <c r="I139" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.52499999999999991</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="L139">
         <v>0</v>
       </c>
       <c r="M139">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0.495</v>
       </c>
       <c r="N139">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.495</v>
       </c>
       <c r="O139">
@@ -16978,21 +16964,21 @@
         <v>21</v>
       </c>
       <c r="I140" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.7</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="L140">
         <v>0</v>
       </c>
       <c r="M140">
-        <f t="shared" ref="M140:M171" si="17">0.33*E140/2000</f>
+        <f t="shared" ref="M140:M171" si="18">0.33*E140/2000</f>
         <v>0.66</v>
       </c>
       <c r="N140">
@@ -17026,21 +17012,21 @@
         <v>51</v>
       </c>
       <c r="I141" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.3999999999999999E-2</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.04</v>
       </c>
       <c r="L141">
         <v>0</v>
       </c>
       <c r="M141">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.3200000000000002E-2</v>
       </c>
       <c r="N141">
@@ -17074,21 +17060,21 @@
         <v>25</v>
       </c>
       <c r="I142" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.0499999999999999E-2</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.03</v>
       </c>
       <c r="L142">
         <v>0</v>
       </c>
       <c r="M142">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="N142">
@@ -17122,25 +17108,25 @@
         <v>47</v>
       </c>
       <c r="I143" s="27">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>8.7499999999999991E-3</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="L143">
         <v>0</v>
       </c>
       <c r="M143">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.2500000000000004E-3</v>
       </c>
       <c r="N143">
-        <f t="shared" ref="N143:N171" si="18">-M143</f>
+        <f t="shared" ref="N143:N171" si="19">-M143</f>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O143">
@@ -17177,18 +17163,18 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4.4499999999999998E-2</v>
       </c>
       <c r="L144">
         <v>0</v>
       </c>
       <c r="M144">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.4685E-2</v>
       </c>
       <c r="N144">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1.4685E-2</v>
       </c>
       <c r="O144">
@@ -17218,25 +17204,25 @@
         <v>25</v>
       </c>
       <c r="I145" s="28">
-        <f t="shared" ref="I145:I171" si="19">0.1*K145</f>
+        <f t="shared" ref="I145:I171" si="20">0.1*K145</f>
         <v>2.7500000000000003E-3</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.75E-2</v>
       </c>
       <c r="L145">
         <v>0</v>
       </c>
       <c r="M145">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.0750000000000015E-3</v>
       </c>
       <c r="N145">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O145">
@@ -17266,25 +17252,25 @@
         <v>25</v>
       </c>
       <c r="I146" s="28">
+        <f t="shared" si="20"/>
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <f t="shared" si="17"/>
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="18"/>
+        <v>2.4420000000000001E-2</v>
+      </c>
+      <c r="N146">
         <f t="shared" si="19"/>
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <f t="shared" si="16"/>
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <f t="shared" si="17"/>
-        <v>2.4420000000000001E-2</v>
-      </c>
-      <c r="N146">
-        <f t="shared" si="18"/>
         <v>-2.4420000000000001E-2</v>
       </c>
       <c r="O146">
@@ -17314,25 +17300,25 @@
         <v>46</v>
       </c>
       <c r="I147" s="28">
+        <f t="shared" si="20"/>
+        <v>2.5000000000000005E-3</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <f t="shared" si="17"/>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="18"/>
+        <v>8.2500000000000004E-3</v>
+      </c>
+      <c r="N147">
         <f t="shared" si="19"/>
-        <v>2.5000000000000005E-3</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <f t="shared" si="16"/>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <f t="shared" si="17"/>
-        <v>8.2500000000000004E-3</v>
-      </c>
-      <c r="N147">
-        <f t="shared" si="18"/>
         <v>-8.2500000000000004E-3</v>
       </c>
       <c r="O147">
@@ -17362,25 +17348,25 @@
         <v>16</v>
       </c>
       <c r="I148" s="28">
+        <f t="shared" si="20"/>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <f t="shared" si="17"/>
+        <v>0.04</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="18"/>
+        <v>1.3200000000000002E-2</v>
+      </c>
+      <c r="N148">
         <f t="shared" si="19"/>
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <f t="shared" si="16"/>
-        <v>0.04</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <f t="shared" si="17"/>
-        <v>1.3200000000000002E-2</v>
-      </c>
-      <c r="N148">
-        <f t="shared" si="18"/>
         <v>-1.3200000000000002E-2</v>
       </c>
       <c r="O148">
@@ -17410,25 +17396,25 @@
         <v>45</v>
       </c>
       <c r="I149" s="28">
+        <f t="shared" si="20"/>
+        <v>3.0500000000000002E-3</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <f t="shared" si="17"/>
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <f t="shared" si="18"/>
+        <v>1.0065000000000001E-2</v>
+      </c>
+      <c r="N149">
         <f t="shared" si="19"/>
-        <v>3.0500000000000002E-3</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <f t="shared" si="16"/>
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <f t="shared" si="17"/>
-        <v>1.0065000000000001E-2</v>
-      </c>
-      <c r="N149">
-        <f t="shared" si="18"/>
         <v>-1.0065000000000001E-2</v>
       </c>
       <c r="O149">
@@ -17465,18 +17451,18 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3.6999999999999998E-2</v>
       </c>
       <c r="L150">
         <v>0</v>
       </c>
       <c r="M150">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.221E-2</v>
       </c>
       <c r="N150">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1.221E-2</v>
       </c>
       <c r="O150">
@@ -17506,25 +17492,25 @@
         <v>23</v>
       </c>
       <c r="I151" s="28">
+        <f t="shared" si="20"/>
+        <v>2.7500000000000003E-3</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <f t="shared" si="17"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <f t="shared" si="18"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N151">
         <f t="shared" si="19"/>
-        <v>2.7500000000000003E-3</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <f t="shared" si="16"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151">
-        <f t="shared" si="17"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N151">
-        <f t="shared" si="18"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O151">
@@ -17554,25 +17540,25 @@
         <v>20</v>
       </c>
       <c r="I152" s="28">
+        <f t="shared" si="20"/>
+        <v>2.7500000000000003E-3</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <f t="shared" si="17"/>
+        <v>2.75E-2</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <f t="shared" si="18"/>
+        <v>9.0750000000000015E-3</v>
+      </c>
+      <c r="N152">
         <f t="shared" si="19"/>
-        <v>2.7500000000000003E-3</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <f t="shared" si="16"/>
-        <v>2.75E-2</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
-        <f t="shared" si="17"/>
-        <v>9.0750000000000015E-3</v>
-      </c>
-      <c r="N152">
-        <f t="shared" si="18"/>
         <v>-9.0750000000000015E-3</v>
       </c>
       <c r="O152">
@@ -17602,25 +17588,25 @@
         <v>19</v>
       </c>
       <c r="I153" s="28">
+        <f t="shared" si="20"/>
+        <v>3.7499999999999999E-3</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <f t="shared" si="17"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <f t="shared" si="18"/>
+        <v>1.2375000000000001E-2</v>
+      </c>
+      <c r="N153">
         <f t="shared" si="19"/>
-        <v>3.7499999999999999E-3</v>
-      </c>
-      <c r="J153">
-        <v>0</v>
-      </c>
-      <c r="K153">
-        <f t="shared" si="16"/>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
-        <f t="shared" si="17"/>
-        <v>1.2375000000000001E-2</v>
-      </c>
-      <c r="N153">
-        <f t="shared" si="18"/>
         <v>-1.2375000000000001E-2</v>
       </c>
       <c r="O153">
@@ -17650,25 +17636,25 @@
         <v>30</v>
       </c>
       <c r="I154" s="28">
+        <f t="shared" si="20"/>
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <f t="shared" si="17"/>
+        <v>2.7E-2</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <f t="shared" si="18"/>
+        <v>8.9099999999999995E-3</v>
+      </c>
+      <c r="N154">
         <f t="shared" si="19"/>
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="J154">
-        <v>0</v>
-      </c>
-      <c r="K154">
-        <f t="shared" si="16"/>
-        <v>2.7E-2</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154">
-        <f t="shared" si="17"/>
-        <v>8.9099999999999995E-3</v>
-      </c>
-      <c r="N154">
-        <f t="shared" si="18"/>
         <v>-8.9099999999999995E-3</v>
       </c>
       <c r="O154">
@@ -17698,25 +17684,25 @@
         <v>9</v>
       </c>
       <c r="I155" s="28">
+        <f t="shared" si="20"/>
+        <v>3.2500000000000003E-3</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <f t="shared" si="17"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <f t="shared" si="18"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N155">
         <f t="shared" si="19"/>
-        <v>3.2500000000000003E-3</v>
-      </c>
-      <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <f t="shared" si="16"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
-        <f t="shared" si="17"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N155">
-        <f t="shared" si="18"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O155" s="5">
@@ -17752,25 +17738,25 @@
         <v>50</v>
       </c>
       <c r="I156" s="28">
+        <f t="shared" si="20"/>
+        <v>3.1000000000000003E-3</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <f t="shared" si="17"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <f t="shared" si="18"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N156">
         <f t="shared" si="19"/>
-        <v>3.1000000000000003E-3</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <f t="shared" si="16"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
-        <f t="shared" si="17"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N156">
-        <f t="shared" si="18"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O156">
@@ -17800,25 +17786,25 @@
         <v>27</v>
       </c>
       <c r="I157" s="28">
+        <f t="shared" si="20"/>
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <f t="shared" si="17"/>
+        <v>4.7E-2</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <f t="shared" si="18"/>
+        <v>1.5510000000000001E-2</v>
+      </c>
+      <c r="N157">
         <f t="shared" si="19"/>
-        <v>4.7000000000000002E-3</v>
-      </c>
-      <c r="J157">
-        <v>0</v>
-      </c>
-      <c r="K157">
-        <f t="shared" si="16"/>
-        <v>4.7E-2</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157">
-        <f t="shared" si="17"/>
-        <v>1.5510000000000001E-2</v>
-      </c>
-      <c r="N157">
-        <f t="shared" si="18"/>
         <v>-1.5510000000000001E-2</v>
       </c>
       <c r="O157">
@@ -17848,25 +17834,25 @@
         <v>20</v>
       </c>
       <c r="I158" s="28">
+        <f t="shared" si="20"/>
+        <v>4.8000000000000004E-3</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <f t="shared" si="17"/>
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <f t="shared" si="18"/>
+        <v>1.584E-2</v>
+      </c>
+      <c r="N158">
         <f t="shared" si="19"/>
-        <v>4.8000000000000004E-3</v>
-      </c>
-      <c r="J158">
-        <v>0</v>
-      </c>
-      <c r="K158">
-        <f t="shared" si="16"/>
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
-        <f t="shared" si="17"/>
-        <v>1.584E-2</v>
-      </c>
-      <c r="N158">
-        <f t="shared" si="18"/>
         <v>-1.584E-2</v>
       </c>
       <c r="O158">
@@ -17896,25 +17882,25 @@
         <v>27</v>
       </c>
       <c r="I159" s="28">
+        <f t="shared" si="20"/>
+        <v>4.3E-3</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <f t="shared" si="17"/>
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <f t="shared" si="18"/>
+        <v>1.4190000000000001E-2</v>
+      </c>
+      <c r="N159">
         <f t="shared" si="19"/>
-        <v>4.3E-3</v>
-      </c>
-      <c r="J159">
-        <v>0</v>
-      </c>
-      <c r="K159">
-        <f t="shared" si="16"/>
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="M159">
-        <f t="shared" si="17"/>
-        <v>1.4190000000000001E-2</v>
-      </c>
-      <c r="N159">
-        <f t="shared" si="18"/>
         <v>-1.4190000000000001E-2</v>
       </c>
       <c r="O159">
@@ -17944,25 +17930,25 @@
         <v>47</v>
       </c>
       <c r="I160" s="28">
+        <f t="shared" si="20"/>
+        <v>6.6000000000000008E-3</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <f t="shared" si="17"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <f t="shared" si="18"/>
+        <v>2.1780000000000001E-2</v>
+      </c>
+      <c r="N160">
         <f t="shared" si="19"/>
-        <v>6.6000000000000008E-3</v>
-      </c>
-      <c r="J160">
-        <v>0</v>
-      </c>
-      <c r="K160">
-        <f t="shared" si="16"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160">
-        <f t="shared" si="17"/>
-        <v>2.1780000000000001E-2</v>
-      </c>
-      <c r="N160">
-        <f t="shared" si="18"/>
         <v>-2.1780000000000001E-2</v>
       </c>
       <c r="O160">
@@ -17992,25 +17978,25 @@
         <v>48</v>
       </c>
       <c r="I161" s="28">
+        <f t="shared" si="20"/>
+        <v>3.2500000000000003E-3</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <f t="shared" si="17"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <f t="shared" si="18"/>
+        <v>1.0725E-2</v>
+      </c>
+      <c r="N161">
         <f t="shared" si="19"/>
-        <v>3.2500000000000003E-3</v>
-      </c>
-      <c r="J161">
-        <v>0</v>
-      </c>
-      <c r="K161">
-        <f t="shared" si="16"/>
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161">
-        <f t="shared" si="17"/>
-        <v>1.0725E-2</v>
-      </c>
-      <c r="N161">
-        <f t="shared" si="18"/>
         <v>-1.0725E-2</v>
       </c>
       <c r="O161">
@@ -18040,25 +18026,25 @@
         <v>27</v>
       </c>
       <c r="I162" s="28">
+        <f t="shared" si="20"/>
+        <v>5.8000000000000005E-3</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <f t="shared" si="17"/>
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="18"/>
+        <v>1.9140000000000001E-2</v>
+      </c>
+      <c r="N162">
         <f t="shared" si="19"/>
-        <v>5.8000000000000005E-3</v>
-      </c>
-      <c r="J162">
-        <v>0</v>
-      </c>
-      <c r="K162">
-        <f t="shared" si="16"/>
-        <v>5.8000000000000003E-2</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162">
-        <f t="shared" si="17"/>
-        <v>1.9140000000000001E-2</v>
-      </c>
-      <c r="N162">
-        <f t="shared" si="18"/>
         <v>-1.9140000000000001E-2</v>
       </c>
       <c r="O162">
@@ -18088,25 +18074,25 @@
         <v>9</v>
       </c>
       <c r="I163" s="28">
+        <f t="shared" si="20"/>
+        <v>3.15E-3</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <f t="shared" si="17"/>
+        <v>3.15E-2</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="18"/>
+        <v>1.0395000000000001E-2</v>
+      </c>
+      <c r="N163">
         <f t="shared" si="19"/>
-        <v>3.15E-3</v>
-      </c>
-      <c r="J163">
-        <v>0</v>
-      </c>
-      <c r="K163">
-        <f t="shared" si="16"/>
-        <v>3.15E-2</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="M163">
-        <f t="shared" si="17"/>
-        <v>1.0395000000000001E-2</v>
-      </c>
-      <c r="N163">
-        <f t="shared" si="18"/>
         <v>-1.0395000000000001E-2</v>
       </c>
       <c r="O163" s="5">
@@ -18142,25 +18128,25 @@
         <v>48</v>
       </c>
       <c r="I164" s="28">
+        <f t="shared" si="20"/>
+        <v>2.9000000000000002E-3</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <f t="shared" si="17"/>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="18"/>
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N164">
         <f t="shared" si="19"/>
-        <v>2.9000000000000002E-3</v>
-      </c>
-      <c r="J164">
-        <v>0</v>
-      </c>
-      <c r="K164">
-        <f t="shared" si="16"/>
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164">
-        <f t="shared" si="17"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N164">
-        <f t="shared" si="18"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O164">
@@ -18190,25 +18176,25 @@
         <v>20</v>
       </c>
       <c r="I165" s="28">
+        <f t="shared" si="20"/>
+        <v>5.7500000000000008E-3</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <f t="shared" si="17"/>
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <f t="shared" si="18"/>
+        <v>1.8975000000000002E-2</v>
+      </c>
+      <c r="N165">
         <f t="shared" si="19"/>
-        <v>5.7500000000000008E-3</v>
-      </c>
-      <c r="J165">
-        <v>0</v>
-      </c>
-      <c r="K165">
-        <f t="shared" si="16"/>
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="M165">
-        <f t="shared" si="17"/>
-        <v>1.8975000000000002E-2</v>
-      </c>
-      <c r="N165">
-        <f t="shared" si="18"/>
         <v>-1.8975000000000002E-2</v>
       </c>
       <c r="O165">
@@ -18238,25 +18224,25 @@
         <v>5</v>
       </c>
       <c r="I166" s="28">
+        <f t="shared" si="20"/>
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <f t="shared" si="17"/>
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <f t="shared" si="18"/>
+        <v>1.7819999999999999E-2</v>
+      </c>
+      <c r="N166">
         <f t="shared" si="19"/>
-        <v>5.4000000000000003E-3</v>
-      </c>
-      <c r="J166">
-        <v>0</v>
-      </c>
-      <c r="K166">
-        <f t="shared" si="16"/>
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166">
-        <f t="shared" si="17"/>
-        <v>1.7819999999999999E-2</v>
-      </c>
-      <c r="N166">
-        <f t="shared" si="18"/>
         <v>-1.7819999999999999E-2</v>
       </c>
       <c r="O166" s="5">
@@ -18292,25 +18278,25 @@
         <v>3</v>
       </c>
       <c r="I167" s="28">
+        <f t="shared" si="20"/>
+        <v>2.65E-3</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <f t="shared" si="17"/>
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <f t="shared" si="18"/>
+        <v>8.745000000000001E-3</v>
+      </c>
+      <c r="N167">
         <f t="shared" si="19"/>
-        <v>2.65E-3</v>
-      </c>
-      <c r="J167">
-        <v>0</v>
-      </c>
-      <c r="K167">
-        <f t="shared" si="16"/>
-        <v>2.6499999999999999E-2</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167">
-        <f t="shared" si="17"/>
-        <v>8.745000000000001E-3</v>
-      </c>
-      <c r="N167">
-        <f t="shared" si="18"/>
         <v>-8.745000000000001E-3</v>
       </c>
       <c r="O167" s="5">
@@ -18346,25 +18332,25 @@
         <v>19</v>
       </c>
       <c r="I168" s="28">
+        <f t="shared" si="20"/>
+        <v>2.9000000000000002E-3</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <f t="shared" si="17"/>
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <f t="shared" si="18"/>
+        <v>9.5700000000000004E-3</v>
+      </c>
+      <c r="N168">
         <f t="shared" si="19"/>
-        <v>2.9000000000000002E-3</v>
-      </c>
-      <c r="J168">
-        <v>0</v>
-      </c>
-      <c r="K168">
-        <f t="shared" si="16"/>
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="L168">
-        <v>0</v>
-      </c>
-      <c r="M168">
-        <f t="shared" si="17"/>
-        <v>9.5700000000000004E-3</v>
-      </c>
-      <c r="N168">
-        <f t="shared" si="18"/>
         <v>-9.5700000000000004E-3</v>
       </c>
       <c r="O168">
@@ -18394,25 +18380,25 @@
         <v>31</v>
       </c>
       <c r="I169" s="28">
+        <f t="shared" si="20"/>
+        <v>3.1000000000000003E-3</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <f t="shared" si="17"/>
+        <v>3.1E-2</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <f t="shared" si="18"/>
+        <v>1.0230000000000001E-2</v>
+      </c>
+      <c r="N169">
         <f t="shared" si="19"/>
-        <v>3.1000000000000003E-3</v>
-      </c>
-      <c r="J169">
-        <v>0</v>
-      </c>
-      <c r="K169">
-        <f t="shared" si="16"/>
-        <v>3.1E-2</v>
-      </c>
-      <c r="L169">
-        <v>0</v>
-      </c>
-      <c r="M169">
-        <f t="shared" si="17"/>
-        <v>1.0230000000000001E-2</v>
-      </c>
-      <c r="N169">
-        <f t="shared" si="18"/>
         <v>-1.0230000000000001E-2</v>
       </c>
       <c r="O169">
@@ -18442,25 +18428,25 @@
         <v>31</v>
       </c>
       <c r="I170" s="28">
+        <f t="shared" si="20"/>
+        <v>6.8000000000000005E-3</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <f t="shared" si="17"/>
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <f t="shared" si="18"/>
+        <v>2.2440000000000002E-2</v>
+      </c>
+      <c r="N170">
         <f t="shared" si="19"/>
-        <v>6.8000000000000005E-3</v>
-      </c>
-      <c r="J170">
-        <v>0</v>
-      </c>
-      <c r="K170">
-        <f t="shared" si="16"/>
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="L170">
-        <v>0</v>
-      </c>
-      <c r="M170">
-        <f t="shared" si="17"/>
-        <v>2.2440000000000002E-2</v>
-      </c>
-      <c r="N170">
-        <f t="shared" si="18"/>
         <v>-2.2440000000000002E-2</v>
       </c>
       <c r="O170">
@@ -18491,25 +18477,25 @@
       </c>
       <c r="H171" s="10"/>
       <c r="I171" s="28">
+        <f t="shared" si="20"/>
+        <v>2.9499999999999999E-3</v>
+      </c>
+      <c r="J171" s="10">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <f t="shared" si="17"/>
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="L171" s="10">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <f t="shared" si="18"/>
+        <v>9.7350000000000006E-3</v>
+      </c>
+      <c r="N171">
         <f t="shared" si="19"/>
-        <v>2.9499999999999999E-3</v>
-      </c>
-      <c r="J171" s="10">
-        <v>0</v>
-      </c>
-      <c r="K171">
-        <f t="shared" si="16"/>
-        <v>2.9499999999999998E-2</v>
-      </c>
-      <c r="L171" s="10">
-        <v>0</v>
-      </c>
-      <c r="M171">
-        <f t="shared" si="17"/>
-        <v>9.7350000000000006E-3</v>
-      </c>
-      <c r="N171">
-        <f t="shared" si="18"/>
         <v>-9.7350000000000006E-3</v>
       </c>
       <c r="O171" s="5">
@@ -18609,7 +18595,7 @@
         <v>272</v>
       </c>
       <c r="E2">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="F2">
         <v>380</v>
@@ -18618,18 +18604,18 @@
         <v>40</v>
       </c>
       <c r="I2" s="31">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <f>E2/2000</f>
-        <v>1.17</v>
+        <f>1.972/2</f>
+        <v>0.98599999999999999</v>
       </c>
       <c r="L2">
         <f>-K2</f>
-        <v>-1.17</v>
+        <v>-0.98599999999999999</v>
       </c>
       <c r="M2">
         <f>5/2</f>
@@ -27022,7 +27008,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="J2">
         <v>380</v>
@@ -27066,7 +27052,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2340</v>
+        <v>1972</v>
       </c>
       <c r="J3">
         <v>380</v>
@@ -27110,7 +27096,7 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="J4">
         <v>380</v>
@@ -27154,7 +27140,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>2340</v>
+        <v>986</v>
       </c>
       <c r="J5">
         <v>380</v>
@@ -27198,7 +27184,7 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="J6">
         <v>380</v>
@@ -27242,7 +27228,7 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>1200</v>
+        <v>1128</v>
       </c>
       <c r="J7">
         <v>380</v>
@@ -27286,7 +27272,7 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>10800</v>
+        <v>1000</v>
       </c>
       <c r="J8">
         <v>380</v>
@@ -27330,7 +27316,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="J9">
         <v>380</v>
@@ -27376,7 +27362,7 @@
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10">
-        <v>11100</v>
+        <v>700</v>
       </c>
       <c r="J10" s="10">
         <v>380</v>
@@ -30623,8 +30609,8 @@
       </c>
       <c r="G83" s="23"/>
       <c r="H83" s="23"/>
-      <c r="I83">
-        <v>2340</v>
+      <c r="I83" s="23">
+        <v>1972</v>
       </c>
       <c r="J83" s="23">
         <v>380</v>
